--- a/DOSSIES_MULTIFORMATO/IDAM/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/IDAM/dossie.xlsx
@@ -636,12 +636,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2023NE0001762</t>
+          <t>2023NE0001759</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16/2018</t>
+          <t>7/2020</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5341.96</v>
+        <v>31820.24</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -659,19 +659,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB PARA PUBLICAÇÃO DE INFORMAÇÕES, NOTÍCIAS, VÍDEO E IMAGENS VIA WEBSITE. TC</t>
+          <t>Contratação de empresa especializada em manter o cadastro dos servidores e folha de pagamento pessoal, processar folhas de pagamento e fornecer relatórios para efetivação de pagamento. TC: 007/2020 AD</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023NE0001760</t>
+          <t>2023NE0001761</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>8/2020</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4946.96</v>
+        <v>93376.48</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -689,19 +689,19 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Contratação de Serviço de execução de sistema de protocolo em plataforma web, objetivando o controle e acompanhamento o controle e acompanhamento do registro de todos os documentos ou processos do cli</t>
+          <t xml:space="preserve">Contratação de empresa especializada em serviço de acesso à rede de internet, para atender as necessidades do Instituto de Desenvolvimento Agropecuário e Florestal Sustentável do Estado do Amazonas – </t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023NE0001761</t>
+          <t>2023NE0001760</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>8/2020</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>93376.48</v>
+        <v>4946.96</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -719,19 +719,19 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de empresa especializada em serviço de acesso à rede de internet, para atender as necessidades do Instituto de Desenvolvimento Agropecuário e Florestal Sustentável do Estado do Amazonas – </t>
+          <t>Contratação de Serviço de execução de sistema de protocolo em plataforma web, objetivando o controle e acompanhamento o controle e acompanhamento do registro de todos os documentos ou processos do cli</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2023NE0001759</t>
+          <t>2023NE0001762</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7/2020</t>
+          <t>16/2018</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>31820.24</v>
+        <v>5341.96</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -749,14 +749,14 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em manter o cadastro dos servidores e folha de pagamento pessoal, processar folhas de pagamento e fornecer relatórios para efetivação de pagamento. TC: 007/2020 AD</t>
+          <t>CONTRATAÇÃO DE SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB PARA PUBLICAÇÃO DE INFORMAÇÕES, NOTÍCIAS, VÍDEO E IMAGENS VIA WEBSITE. TC</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2018NE00975</t>
+          <t>2018NE00976</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>25200</v>
+        <v>1684.48</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -775,14 +775,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-ANULAÇÃO PARCIAL QUE SE FAZ DA NE º 335/2018, EM VIRTUDE DO ENCERRAMENTO DA VIGÊNCIA DO CONTRATO Nº 013/2017</t>
+          <t>ANULAÇÃO PARCIAL QUE SE FAZ DA NOTA DE EMPENHO DE Nº 334/2018, EM VIRTUDE DO TERMINO DA VIGENCIA DO CONTRATO DE Nº 04/2015</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2018NE00976</t>
+          <t>2018NE00975</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1684.48</v>
+        <v>25200</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL QUE SE FAZ DA NOTA DE EMPENHO DE Nº 334/2018, EM VIRTUDE DO TERMINO DA VIGENCIA DO CONTRATO DE Nº 04/2015</t>
+          <t>-ANULAÇÃO PARCIAL QUE SE FAZ DA NE º 335/2018, EM VIRTUDE DO ENCERRAMENTO DA VIGÊNCIA DO CONTRATO Nº 013/2017</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2018NE00049</t>
+          <t>2018NE00050</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3/2015</t>
+          <t>4/2015</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>21277.08</v>
+        <v>49697.78</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-REFERENTE A PARTE DO TERCEIRO TERMO ADITIVO AO TERMO DE CONTRATO DE Nº 003/2015, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS - IDAM E A EMP</t>
+          <t>-REFERENTE A PARTE DO TERCEIRO TERMO ADITIVO AO TERMO DE CONTRATO Nº 004/2015, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS - IDAM E A EMPRES</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2018NE00050</t>
+          <t>2018NE00049</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4/2015</t>
+          <t>3/2015</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>49697.78</v>
+        <v>21277.08</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -891,19 +891,19 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-REFERENTE A PARTE DO TERCEIRO TERMO ADITIVO AO TERMO DE CONTRATO Nº 004/2015, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS - IDAM E A EMPRES</t>
+          <t>-REFERENTE A PARTE DO TERCEIRO TERMO ADITIVO AO TERMO DE CONTRATO DE Nº 003/2015, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS - IDAM E A EMP</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2017NE00054</t>
+          <t>2017NE00055</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4/2015</t>
+          <t>3/2015</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -912,7 +912,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13553.94</v>
+        <v>5802.84</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -921,19 +921,19 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-REFERENTE A PARTE DO SEGUNDO TERMO ADITIVO AO TERMO DE CONTRATO Nº 004/2015, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS - IDAM E A EMPRESA</t>
+          <t>-REFERENTE A PARTE DO SEGUNDO TERMO ADITIVO AO TERMO DE CONTRATO DE Nº 003/2015, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS - IDAM E A EMPR</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2017NE00055</t>
+          <t>2017NE00054</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>3/2015</t>
+          <t>4/2015</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>5802.84</v>
+        <v>13553.94</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -951,14 +951,14 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-REFERENTE A PARTE DO SEGUNDO TERMO ADITIVO AO TERMO DE CONTRATO DE Nº 003/2015, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS - IDAM E A EMPR</t>
+          <t>-REFERENTE A PARTE DO SEGUNDO TERMO ADITIVO AO TERMO DE CONTRATO Nº 004/2015, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS - IDAM E A EMPRESA</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2020NE01696</t>
+          <t>2020NE01697</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -968,7 +968,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>9565.709999999999</v>
+        <v>9008.690000000001</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL QUE SE FAZ DA NE Nº 099/2020, EM VIRTUDE DO ENCERRAMENTO DO EXERCÍCIO DE 2020.</t>
+          <t>ANULAÇÃO PARCIAL QUE SE FAZ DA NE Nº 00100/2020, EM VIRTUDE DO ENCERRAMENTO DO EXERCÍCIO DE 2020.</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2020NE01697</t>
+          <t>2020NE01696</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>9008.690000000001</v>
+        <v>9565.709999999999</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL QUE SE FAZ DA NE Nº 00100/2020, EM VIRTUDE DO ENCERRAMENTO DO EXERCÍCIO DE 2020.</t>
+          <t>ANULAÇÃO PARCIAL QUE SE FAZ DA NE Nº 099/2020, EM VIRTUDE DO ENCERRAMENTO DO EXERCÍCIO DE 2020.</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2017NE01695</t>
+          <t>2017NE01696</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1270,7 +1270,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>4517.98</v>
+        <v>529.46</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1279,14 +1279,14 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-ANULAÇÃO DO SALDO TOTAL DA NOTA DE EMPENHO Nº 1424/2017, EM VIRTUDE DO ENCERRAMENTO DO EXERCÍCIO DE 2017.</t>
+          <t>-ANULAÇÃO DO SALDO TOTAL DA NOTA DE EMPENHO Nº 1446/2017, EM VIRTUDE DO ENCERRAMENTO DO EXERCÍCIO DE 2017.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2017NE01697</t>
+          <t>2017NE01698</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1305,14 +1305,14 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-ANULAÇÃO DO SALDO TOTAL DA NOTA DE EMPENHO Nº 1469/2017, EM VIRTUDE DO ENCERRAMENTO DO EXERCÍCIO DE 2017.</t>
+          <t>-ANULAÇÃO DO SALDO TOTAL DA NOTA DE EMPENHO Nº 1609/2017, EM VIRTUDE DO ENCERRAMENTO DO EXERCÍCIO DE 2017.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2017NE01693</t>
+          <t>2017NE01694</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1322,7 +1322,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>3033</v>
+        <v>6758.37</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1331,14 +1331,14 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-ANULAÇÃO DO SALDO TOTAL DA NOTA DE EMPENHO Nº 0815/2017, EM VIRTUDE DO ENCERRAMENTO DO EXERCÍCIO DE 2017.</t>
+          <t>-ANULAÇÃO DO SALDO TOTAL DA NOTA DE EMPENHO Nº 0957/2017, EM VIRTUDE DO ENCERRAMENTO DO EXERCÍCIO DE 2017.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2017NE01692</t>
+          <t>2017NE01700</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>145.05</v>
+        <v>4517.98</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1357,14 +1357,14 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-ANULAÇÃO DO SALDO TOTAL DA NOTA DE EMPENHO Nº 055/2017, EM VIRTUDE DO ENCERRAMENTO DO EXERCÍCIO DE 2017.</t>
+          <t>-ANULAÇÃO DO SALDO TOTAL DA NOTA DE EMPENHO Nº 1621/2017, EM VIRTUDE DO ENCERRAMENTO DO EXERCÍCIO DE 2017.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2017NE01689</t>
+          <t>2017NE01699</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>333.99</v>
+        <v>12600</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1383,14 +1383,14 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-ANULAÇÃO DO SALDO TOTAL DA NOTA DE EMPENHO Nº 006/2017, EM VIRTUDE DO ENCERRAMENTO DO EXERCÍCIO DE 2017.</t>
+          <t>-ANULAÇÃO DO SALDO TOTAL DA NOTA DE EMPENHO Nº 1615/2017, EM VIRTUDE DO ENCERRAMENTO DO EXERCÍCIO DE 2017.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2017NE01688</t>
+          <t>2017NE01691</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>4488.4</v>
+        <v>39981.11</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-ANULAÇÃO DO SALDO TOTAL DA NOTA DE EMPENHO Nº 005/2017, EM VIRTUDE DO ENCERRAMENTO DO EXERCÍCIO DE 2017.</t>
+          <t>-ANULAÇÃO DO SALDO TOTAL DA NOTA DE EMPENHO Nº 048/2017, EM VIRTUDE DO ENCERRAMENTO DO EXERCÍCIO DE 2017.</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2017NE01691</t>
+          <t>2017NE01688</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>39981.11</v>
+        <v>4488.4</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1461,14 +1461,14 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-ANULAÇÃO DO SALDO TOTAL DA NOTA DE EMPENHO Nº 048/2017, EM VIRTUDE DO ENCERRAMENTO DO EXERCÍCIO DE 2017.</t>
+          <t>-ANULAÇÃO DO SALDO TOTAL DA NOTA DE EMPENHO Nº 005/2017, EM VIRTUDE DO ENCERRAMENTO DO EXERCÍCIO DE 2017.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2017NE01699</t>
+          <t>2017NE01689</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1478,7 +1478,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12600</v>
+        <v>333.99</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1487,14 +1487,14 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-ANULAÇÃO DO SALDO TOTAL DA NOTA DE EMPENHO Nº 1615/2017, EM VIRTUDE DO ENCERRAMENTO DO EXERCÍCIO DE 2017.</t>
+          <t>-ANULAÇÃO DO SALDO TOTAL DA NOTA DE EMPENHO Nº 006/2017, EM VIRTUDE DO ENCERRAMENTO DO EXERCÍCIO DE 2017.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2017NE01700</t>
+          <t>2017NE01692</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1504,7 +1504,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>4517.98</v>
+        <v>145.05</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1513,14 +1513,14 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-ANULAÇÃO DO SALDO TOTAL DA NOTA DE EMPENHO Nº 1621/2017, EM VIRTUDE DO ENCERRAMENTO DO EXERCÍCIO DE 2017.</t>
+          <t>-ANULAÇÃO DO SALDO TOTAL DA NOTA DE EMPENHO Nº 055/2017, EM VIRTUDE DO ENCERRAMENTO DO EXERCÍCIO DE 2017.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2017NE01694</t>
+          <t>2017NE01693</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>6758.37</v>
+        <v>3033</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1539,14 +1539,14 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-ANULAÇÃO DO SALDO TOTAL DA NOTA DE EMPENHO Nº 0957/2017, EM VIRTUDE DO ENCERRAMENTO DO EXERCÍCIO DE 2017.</t>
+          <t>-ANULAÇÃO DO SALDO TOTAL DA NOTA DE EMPENHO Nº 0815/2017, EM VIRTUDE DO ENCERRAMENTO DO EXERCÍCIO DE 2017.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2017NE01698</t>
+          <t>2017NE01697</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1565,14 +1565,14 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-ANULAÇÃO DO SALDO TOTAL DA NOTA DE EMPENHO Nº 1609/2017, EM VIRTUDE DO ENCERRAMENTO DO EXERCÍCIO DE 2017.</t>
+          <t>-ANULAÇÃO DO SALDO TOTAL DA NOTA DE EMPENHO Nº 1469/2017, EM VIRTUDE DO ENCERRAMENTO DO EXERCÍCIO DE 2017.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2017NE01696</t>
+          <t>2017NE01695</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>529.46</v>
+        <v>4517.98</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1591,21 +1591,17 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-ANULAÇÃO DO SALDO TOTAL DA NOTA DE EMPENHO Nº 1446/2017, EM VIRTUDE DO ENCERRAMENTO DO EXERCÍCIO DE 2017.</t>
+          <t>-ANULAÇÃO DO SALDO TOTAL DA NOTA DE EMPENHO Nº 1424/2017, EM VIRTUDE DO ENCERRAMENTO DO EXERCÍCIO DE 2017.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2022NE0003048</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>16/2018</t>
-        </is>
-      </c>
+          <t>2022NE0003050</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
           <t>29/11/2022</t>
@@ -1621,17 +1617,21 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB PARA PUBLICAÇÃO DE INFORMAÇÕES, NOTÍCIAS, VÍDEO E IMAGENS VIA WEBSITE.</t>
+          <t>ANULAÇÃO TOTAL QUE SE FAZ DA NE Nº 3033/2022. PARA AJUSTE ORÇAMENTÁRIO.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2022NE0003050</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
+          <t>2022NE0003048</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>16/2018</t>
+        </is>
+      </c>
       <c r="C38" t="inlineStr">
         <is>
           <t>29/11/2022</t>
@@ -1647,14 +1647,14 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL QUE SE FAZ DA NE Nº 3033/2022. PARA AJUSTE ORÇAMENTÁRIO.</t>
+          <t>CONTRATAÇÃO DE SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB PARA PUBLICAÇÃO DE INFORMAÇÕES, NOTÍCIAS, VÍDEO E IMAGENS VIA WEBSITE.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2016NE01680</t>
+          <t>2016NE01677</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1684,21 +1684,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2016NE01679</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>4/2015</t>
-        </is>
-      </c>
+          <t>2016NE01678</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
           <t>29/11/2016</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>4517.98</v>
+        <v>7015.13</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1707,24 +1703,28 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-REFERENTE A PARTE DO PRIMEIRO TERMO ADITIVO AO TERMO DE CONTRATO Nº 004/2015, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS - IDAM E A EMPRES</t>
+          <t>ANULAÇÃO TOTAL QUE SE FAZ DA NOTA DE EMPENHO DE Nº 1677/2016, EM VIRTUDE DE EQUIVOCO NO PROJETO DE ATIVIDADE DO REFERIDO EMPENHO</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2016NE01678</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
+          <t>2016NE01679</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>4/2015</t>
+        </is>
+      </c>
       <c r="C41" t="inlineStr">
         <is>
           <t>29/11/2016</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>7015.13</v>
+        <v>4517.98</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1733,14 +1733,14 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL QUE SE FAZ DA NOTA DE EMPENHO DE Nº 1677/2016, EM VIRTUDE DE EQUIVOCO NO PROJETO DE ATIVIDADE DO REFERIDO EMPENHO</t>
+          <t>-REFERENTE A PARTE DO PRIMEIRO TERMO ADITIVO AO TERMO DE CONTRATO Nº 004/2015, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS - IDAM E A EMPRES</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2016NE01677</t>
+          <t>2016NE01680</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1800,12 +1800,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2016NE00296</t>
+          <t>2016NE00292</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>4/2015</t>
+          <t>3/2015</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1814,7 +1814,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1405.92</v>
+        <v>1165.85</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1823,19 +1823,19 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Custear despesas de exercício anterior com serviços de execução de sistemas Recursos Humanos e Folha - novembro. Contrato nº 004/2015</t>
+          <t>Custear despesas de exercício anterior com serviços de execução de sistemas Controle de Protocolo. Contrato nº 003/2015</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2016NE00295</t>
+          <t>2016NE00293</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>3/2015</t>
+          <t>4/2015</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1844,7 +1844,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1157.9</v>
+        <v>2572.23</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1853,19 +1853,19 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Custear despesas de exercício anterior com serviços de execução de sistemas Controle de Protocolo - dezembro. Contrato nº 003/2015</t>
+          <t>Custear despesas de exercício anterior com serviços de execução de sistemas Recursos Humanos e Folha - dezembro. Contrato nº 004/2015</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2016NE00293</t>
+          <t>2016NE00295</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>4/2015</t>
+          <t>3/2015</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>2572.23</v>
+        <v>1157.9</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1883,19 +1883,19 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Custear despesas de exercício anterior com serviços de execução de sistemas Recursos Humanos e Folha - dezembro. Contrato nº 004/2015</t>
+          <t>Custear despesas de exercício anterior com serviços de execução de sistemas Controle de Protocolo - dezembro. Contrato nº 003/2015</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2016NE00292</t>
+          <t>2016NE00296</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>3/2015</t>
+          <t>4/2015</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1165.85</v>
+        <v>1405.92</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Custear despesas de exercício anterior com serviços de execução de sistemas Controle de Protocolo. Contrato nº 003/2015</t>
+          <t>Custear despesas de exercício anterior com serviços de execução de sistemas Recursos Humanos e Folha - novembro. Contrato nº 004/2015</t>
         </is>
       </c>
     </row>
@@ -1976,7 +1976,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2018NE01850</t>
+          <t>2018NE01849</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -1995,14 +1995,14 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-ANULAÇÃO TOTAL QUE SE FAZ DA NE Nº 1600/2018, PARA AJUSTE ORÇAMENTÁRIO 2018 E EM CUMPRIMENTO AO ART 42 DA LRF.</t>
+          <t>-ANULAÇÃO PARCIAL QUE SE FAZ DA NE Nº 1317/2018, PARA AJUSTE ORÇAMENTÁRIO 2018 E EM CUMPRIMENTO AO ART 42 DA LRF.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2018NE01864</t>
+          <t>2018NE01865</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>5523.44</v>
+        <v>1895.08</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2021,14 +2021,14 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-ANULAÇÃO TOTAL QUE SE FAZ DA NE Nº 0338/2018, PARA AJUSTE ORÇAMENTÁRIO E EM CUMPRIMENTO AO ART. 42 DA LRF.</t>
+          <t>-ANULAÇÃO TOTAL QUE SE FAZ DA NE Nº 0339/2018, PARA AJUSTE ORÇAMENTÁRIO E EM CUMPRIMENTO AO ART. 42 DA LRF.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2018NE01870</t>
+          <t>2018NE01848</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2038,7 +2038,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>15579.88</v>
+        <v>128.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2047,14 +2047,14 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CANCELAMENTO DE SALDO DE EMPENHO A LIQUIDAR PARA AJUSTE ORÇAMENTÁRIO DE ENCERRAMENTO DO EXERCÍCIO DE 2018, EM CUMPRIMENTO AO ART. 42 DA LEI COMPLEMENTAR FEDERAL 101/2000 ( LEI DE RESPONSABILIDADE FISC</t>
+          <t>-ANULAÇÃO TOTAL QUE SE FAZ DA NE Nº 1121/2018, PARA AJUSTE ORÇAMENTÁRIO 2018 E EM CUMPRIMENTO AO ART 42 DA LRF.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2018NE01846</t>
+          <t>2018NE01847</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2064,7 +2064,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>30422.34</v>
+        <v>10138.06</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2073,14 +2073,14 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>-ANULAÇÃO PARCIAL QUE SE FAZ DA NE Nº 338/2018, PARA AJUSTE ORÇAMENTÁRIO 2018 E EM CUMPRIMENTO AO ART 42 DA LRF.</t>
+          <t>-ANULAÇÃO PARCIAL QUE SE FAZ DA NE Nº 339/2018, PARA AJUSTE ORÇAMENTÁRIO 2018 E EM CUMPRIMENTO AO ART 42 DA LRF.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2018NE01847</t>
+          <t>2018NE01846</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10138.06</v>
+        <v>30422.34</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2099,14 +2099,14 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>-ANULAÇÃO PARCIAL QUE SE FAZ DA NE Nº 339/2018, PARA AJUSTE ORÇAMENTÁRIO 2018 E EM CUMPRIMENTO AO ART 42 DA LRF.</t>
+          <t>-ANULAÇÃO PARCIAL QUE SE FAZ DA NE Nº 338/2018, PARA AJUSTE ORÇAMENTÁRIO 2018 E EM CUMPRIMENTO AO ART 42 DA LRF.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2018NE01848</t>
+          <t>2018NE01870</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2116,7 +2116,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>128.4</v>
+        <v>15579.88</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2125,14 +2125,14 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>-ANULAÇÃO TOTAL QUE SE FAZ DA NE Nº 1121/2018, PARA AJUSTE ORÇAMENTÁRIO 2018 E EM CUMPRIMENTO AO ART 42 DA LRF.</t>
+          <t>CANCELAMENTO DE SALDO DE EMPENHO A LIQUIDAR PARA AJUSTE ORÇAMENTÁRIO DE ENCERRAMENTO DO EXERCÍCIO DE 2018, EM CUMPRIMENTO AO ART. 42 DA LEI COMPLEMENTAR FEDERAL 101/2000 ( LEI DE RESPONSABILIDADE FISC</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2018NE01865</t>
+          <t>2018NE01864</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2142,7 +2142,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1895.08</v>
+        <v>5523.44</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2151,14 +2151,14 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>-ANULAÇÃO TOTAL QUE SE FAZ DA NE Nº 0339/2018, PARA AJUSTE ORÇAMENTÁRIO E EM CUMPRIMENTO AO ART. 42 DA LRF.</t>
+          <t>-ANULAÇÃO TOTAL QUE SE FAZ DA NE Nº 0338/2018, PARA AJUSTE ORÇAMENTÁRIO E EM CUMPRIMENTO AO ART. 42 DA LRF.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2018NE01849</t>
+          <t>2018NE01850</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>-ANULAÇÃO PARCIAL QUE SE FAZ DA NE Nº 1317/2018, PARA AJUSTE ORÇAMENTÁRIO 2018 E EM CUMPRIMENTO AO ART 42 DA LRF.</t>
+          <t>-ANULAÇÃO TOTAL QUE SE FAZ DA NE Nº 1600/2018, PARA AJUSTE ORÇAMENTÁRIO 2018 E EM CUMPRIMENTO AO ART 42 DA LRF.</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2022NE0003187</t>
+          <t>2022NE0003203</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2280,7 +2280,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>4516.1</v>
+        <v>3358.51</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>ANULAÇÃO EM VIRTUDE DO ENCERRAMENTO DO EXERCICIO DE 2022.</t>
+          <t>ANULAÇÃO PARCIAL EM VIRTUDE DO ENCERRAMENTO DO EXERCICIO DE 2022.</t>
         </is>
       </c>
     </row>
@@ -2322,7 +2322,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2022NE0003203</t>
+          <t>2022NE0003187</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>3358.51</v>
+        <v>4516.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2341,19 +2341,19 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL EM VIRTUDE DO ENCERRAMENTO DO EXERCICIO DE 2022.</t>
+          <t>ANULAÇÃO EM VIRTUDE DO ENCERRAMENTO DO EXERCICIO DE 2022.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2015NE01826</t>
+          <t>2015NE01828</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>8/2012</t>
+          <t>14/2013</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2362,7 +2362,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12676.42</v>
+        <v>18558.9</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2371,19 +2371,19 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>-REFERENTE A PARTE DO TERCEIRO TERMO ADITIVO AO TERMO DE CONTRATO DE Nº 008/2012, FIRMADO ENTRE O ESTE IDAM E A EMPRESA PRODAM PROCESSAMENTO DE DADOS DO AMAZONAS S.A.</t>
+          <t>-REFERENTE A PARTE DO SEGUNDO TERMO ADITIVO AO TERMO DE CONTRATO DE Nº 014/2013, FIRMADO ENTRE O ESTE IDAM E A EMPRESA PRODAM PROCESSAMENTO DE DADOS DO AMAZONAS S.A.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2015NE01828</t>
+          <t>2015NE01826</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>14/2013</t>
+          <t>8/2012</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>18558.9</v>
+        <v>12676.42</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2401,19 +2401,19 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>-REFERENTE A PARTE DO SEGUNDO TERMO ADITIVO AO TERMO DE CONTRATO DE Nº 014/2013, FIRMADO ENTRE O ESTE IDAM E A EMPRESA PRODAM PROCESSAMENTO DE DADOS DO AMAZONAS S.A.</t>
+          <t>-REFERENTE A PARTE DO TERCEIRO TERMO ADITIVO AO TERMO DE CONTRATO DE Nº 008/2012, FIRMADO ENTRE O ESTE IDAM E A EMPRESA PRODAM PROCESSAMENTO DE DADOS DO AMAZONAS S.A.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2017NE01446</t>
+          <t>2017NE01424</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>3/2015</t>
+          <t>4/2015</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1934.28</v>
+        <v>4517.98</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>-REFERENTE A PARTE DO SEGUNDO TERMO ADITIVO AO TERMO DE CONTRATO DE Nº 003/2015, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS - IDAM E A EMPR</t>
+          <t>-REFERENTE A PARTE DO SEGUNDO TERMO ADITIVO AO TERMO DE CONTRATO Nº 004/2015, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS - IDAM E A EMPRESA</t>
         </is>
       </c>
     </row>
@@ -2468,12 +2468,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2017NE01424</t>
+          <t>2017NE01446</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>4/2015</t>
+          <t>3/2015</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2482,7 +2482,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>4517.98</v>
+        <v>1934.28</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>-REFERENTE A PARTE DO SEGUNDO TERMO ADITIVO AO TERMO DE CONTRATO Nº 004/2015, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS - IDAM E A EMPRESA</t>
+          <t>-REFERENTE A PARTE DO SEGUNDO TERMO ADITIVO AO TERMO DE CONTRATO DE Nº 003/2015, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS - IDAM E A EMPR</t>
         </is>
       </c>
     </row>
@@ -2588,12 +2588,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2024NE0000137</t>
+          <t>2024NE0000134</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>7/2020</t>
+          <t>8/2020</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2602,7 +2602,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>18953.73</v>
+        <v>3710.22</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2611,21 +2611,17 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em manter o cadastro dos servidores e folha de pagamento pessoal, processar folhas de pagamento e fornecer relatórios para efetivação de pagamento. TC: 0007/2020 A</t>
+          <t>Contratação de Serviço de execução de sistema de protocolo em plataforma web, objetivando o controle e acompanhamento o controle e acompanhamento do registro de todos os documentos ou processos do cli</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2024NE0000136</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>8/2020</t>
-        </is>
-      </c>
+          <t>2024NE0000135</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
           <t>27/02/2024</t>
@@ -2641,17 +2637,21 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Contratação de Serviço de execução de sistema de protocolo em plataforma web, objetivando o controle e acompanhamento o controle e acompanhamento do registro de todos os documentos ou processos do cli</t>
+          <t>Correção da modalidade do Empenho.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2024NE0000135</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr"/>
+          <t>2024NE0000136</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>8/2020</t>
+        </is>
+      </c>
       <c r="C74" t="inlineStr">
         <is>
           <t>27/02/2024</t>
@@ -2667,19 +2667,19 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Correção da modalidade do Empenho.</t>
+          <t>Contratação de Serviço de execução de sistema de protocolo em plataforma web, objetivando o controle e acompanhamento o controle e acompanhamento do registro de todos os documentos ou processos do cli</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2024NE0000134</t>
+          <t>2024NE0000137</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>8/2020</t>
+          <t>7/2020</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2688,7 +2688,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>3710.22</v>
+        <v>18953.73</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2697,17 +2697,21 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Contratação de Serviço de execução de sistema de protocolo em plataforma web, objetivando o controle e acompanhamento o controle e acompanhamento do registro de todos os documentos ou processos do cli</t>
+          <t>Contratação de empresa especializada em manter o cadastro dos servidores e folha de pagamento pessoal, processar folhas de pagamento e fornecer relatórios para efetivação de pagamento. TC: 0007/2020 A</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2022NE0000058</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr"/>
+          <t>2022NE0000057</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>13/2017</t>
+        </is>
+      </c>
       <c r="C76" t="inlineStr">
         <is>
           <t>27/01/2022</t>
@@ -2723,21 +2727,17 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>-ANULAÇÃO QUE SE FAZ DA NE Nº 57 EM VIRTUDE DO EQUIVOCO DA DATA</t>
+          <t>Contratação de empresa especializada em serviços de acesso a rede de internet, estabelecendo comunicação a partir de circuito de dados existentes entre a contratante e a contratada.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2022NE0000057</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>13/2017</t>
-        </is>
-      </c>
+          <t>2022NE0000058</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
           <t>27/01/2022</t>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviços de acesso a rede de internet, estabelecendo comunicação a partir de circuito de dados existentes entre a contratante e a contratada.</t>
+          <t>-ANULAÇÃO QUE SE FAZ DA NE Nº 57 EM VIRTUDE DO EQUIVOCO DA DATA</t>
         </is>
       </c>
     </row>
@@ -2842,7 +2842,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2018NE00316</t>
+          <t>2018NE00311</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>39921.95</v>
+        <v>10257.48</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -2861,14 +2861,14 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>-ANULAÇÃO TOTAL QUE SE FAZ DA NE Nº0054 DO CONTRATO Nº 023/2015 EM VIRTUDE DA ORIENTAÇÃO DA SEFAZ PARA A TROCA DE NATUREZA DE DESPESA</t>
+          <t>-ANULAÇÃO TOTAL QUE SE FAZ DA NE Nº 0035 DO CONTRATO Nº 017/2014 FIRMADO ENTRE O IDAM E A PRODAM.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2018NE00315</t>
+          <t>2018NE00313</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -2878,7 +2878,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>49697.78</v>
+        <v>4517.98</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -2887,14 +2887,14 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>-ANULAÇÃO TOTAL QUE SE FAZ DA NE Nº0050 DO CONTRATO Nº 003/2015 EM VIRTUDE DA ORIENTAÇÃO DA SEFAZ PARA A TROCA DE NATUREZA DE DESPESA</t>
+          <t>-ANULAÇÃO TOTAL QUE SE FAZ DA NE Nº 0037 DO CONTRATO Nº 004/2015 FIRMADO ENTRE O IDAM E A PRODAM.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2018NE00312</t>
+          <t>2018NE00314</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -2904,7 +2904,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1934.28</v>
+        <v>21277.08</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -2913,14 +2913,14 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>-ANULAÇÃO TOTAL QUE SE FAZ DA NE Nº 0036 DO CONTRATO Nº 003/2015 FIRMADO ENTRE O IDAM E A PRODAM.</t>
+          <t>-ANULAÇÃO TOTAL QUE SE FAZ DA NE Nº0049 DO CONTRATO Nº 003/2015 FIRMADO ENTRE O IDAM E A PRODAM.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2018NE00314</t>
+          <t>2018NE00312</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -2930,7 +2930,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>21277.08</v>
+        <v>1934.28</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -2939,14 +2939,14 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>-ANULAÇÃO TOTAL QUE SE FAZ DA NE Nº0049 DO CONTRATO Nº 003/2015 FIRMADO ENTRE O IDAM E A PRODAM.</t>
+          <t>-ANULAÇÃO TOTAL QUE SE FAZ DA NE Nº 0036 DO CONTRATO Nº 003/2015 FIRMADO ENTRE O IDAM E A PRODAM.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2018NE00313</t>
+          <t>2018NE00315</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -2956,7 +2956,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>4517.98</v>
+        <v>49697.78</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -2965,14 +2965,14 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>-ANULAÇÃO TOTAL QUE SE FAZ DA NE Nº 0037 DO CONTRATO Nº 004/2015 FIRMADO ENTRE O IDAM E A PRODAM.</t>
+          <t>-ANULAÇÃO TOTAL QUE SE FAZ DA NE Nº0050 DO CONTRATO Nº 003/2015 EM VIRTUDE DA ORIENTAÇÃO DA SEFAZ PARA A TROCA DE NATUREZA DE DESPESA</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2018NE00311</t>
+          <t>2018NE00316</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10257.48</v>
+        <v>39921.95</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -2991,17 +2991,21 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>-ANULAÇÃO TOTAL QUE SE FAZ DA NE Nº 0035 DO CONTRATO Nº 017/2014 FIRMADO ENTRE O IDAM E A PRODAM.</t>
+          <t>-ANULAÇÃO TOTAL QUE SE FAZ DA NE Nº0054 DO CONTRATO Nº 023/2015 EM VIRTUDE DA ORIENTAÇÃO DA SEFAZ PARA A TROCA DE NATUREZA DE DESPESA</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2016NE00290</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr"/>
+          <t>2016NE00279</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>8/2012</t>
+        </is>
+      </c>
       <c r="C87" t="inlineStr">
         <is>
           <t>26/02/2016</t>
@@ -3017,7 +3021,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>-ANULAÇÃO TOTAL QUE SE FAZ DA NOTA DE EMPENHO DE Nº 279/2016, EM VIRTUDE DO EQUIVOCO NO CRONOGRAMA DO REFERIDO EMPENHO.</t>
+          <t>-REFERENTE PARTE DO QUARTO TERMO ADITIVO AO TERMO DE CONTRATO Nº 008/2012 FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS - IDAM E A EMPRESA: PR</t>
         </is>
       </c>
     </row>
@@ -3054,14 +3058,10 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2016NE00279</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>8/2012</t>
-        </is>
-      </c>
+          <t>2016NE00290</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
         <is>
           <t>26/02/2016</t>
@@ -3077,17 +3077,21 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>-REFERENTE PARTE DO QUARTO TERMO ADITIVO AO TERMO DE CONTRATO Nº 008/2012 FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS - IDAM E A EMPRESA: PR</t>
+          <t>-ANULAÇÃO TOTAL QUE SE FAZ DA NOTA DE EMPENHO DE Nº 279/2016, EM VIRTUDE DO EQUIVOCO NO CRONOGRAMA DO REFERIDO EMPENHO.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2022NE0000042</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr"/>
+          <t>2022NE0000041</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>13/2017</t>
+        </is>
+      </c>
       <c r="C90" t="inlineStr">
         <is>
           <t>26/01/2022</t>
@@ -3103,21 +3107,17 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>-EQUIVOCO EM VIRTUDE DA DATA</t>
+          <t>Contratação de empresa especializada em serviços de acesso a rede de internet, estabelecendo comunicação a partir de circuito de dados existentes entre a contratante e a contratada.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2022NE0000041</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>13/2017</t>
-        </is>
-      </c>
+          <t>2022NE0000042</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
         <is>
           <t>26/01/2022</t>
@@ -3133,14 +3133,14 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviços de acesso a rede de internet, estabelecendo comunicação a partir de circuito de dados existentes entre a contratante e a contratada.</t>
+          <t>-EQUIVOCO EM VIRTUDE DA DATA</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2015NE00082</t>
+          <t>2015NE00084</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3154,7 +3154,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>16360.23</v>
+        <v>9035.879999999999</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3163,14 +3163,14 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>-ANULAÇÃO TOTAL QUE SE FAZ DA NOTA DE EMPENHO Nº 67 EMITIDA EM 05/01/2015.</t>
+          <t>PRODAM-RH</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2015NE00079</t>
+          <t>2015NE00080</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3193,7 +3193,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>-ANULAÇÃO TOTAL QUE SE FAZ DA NOTA DE EMPENHO Nº 68 EMITIDA EM 05/01/2015, POR EQUIVOCO NA DATA DE EMISSAO.</t>
+          <t>cobertura fevereiro e março 2015</t>
         </is>
       </c>
     </row>
@@ -3230,7 +3230,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2015NE00080</t>
+          <t>2015NE00079</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3253,14 +3253,14 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>cobertura fevereiro e março 2015</t>
+          <t>-ANULAÇÃO TOTAL QUE SE FAZ DA NOTA DE EMPENHO Nº 68 EMITIDA EM 05/01/2015, POR EQUIVOCO NA DATA DE EMISSAO.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2015NE00084</t>
+          <t>2015NE00082</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3274,7 +3274,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>9035.879999999999</v>
+        <v>16360.23</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>PRODAM-RH</t>
+          <t>-ANULAÇÃO TOTAL QUE SE FAZ DA NOTA DE EMPENHO Nº 67 EMITIDA EM 05/01/2015.</t>
         </is>
       </c>
     </row>
@@ -3376,12 +3376,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2022NE0002979</t>
+          <t>2022NE0002978</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>7/2020</t>
+          <t>13/2017</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3390,7 +3390,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>7511.86</v>
+        <v>17876.75</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em manter o cadastro dos servidores e folha de pagamento pessoal, processar folhas de pagamento e fornecer relatórios para efetivação de pagamento.</t>
+          <t>Contratação de empresa especializada em serviços de acesso a rede de internet, estabelecendo comunicação a partir de circuito de dados existentes entre a contratante e a contratada.</t>
         </is>
       </c>
     </row>
@@ -3436,12 +3436,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2022NE0002978</t>
+          <t>2022NE0002979</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>13/2017</t>
+          <t>7/2020</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>17876.75</v>
+        <v>7511.86</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3459,19 +3459,19 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviços de acesso a rede de internet, estabelecendo comunicação a partir de circuito de dados existentes entre a contratante e a contratada.</t>
+          <t>Contratação de empresa especializada em manter o cadastro dos servidores e folha de pagamento pessoal, processar folhas de pagamento e fornecer relatórios para efetivação de pagamento.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2022NE0002181</t>
+          <t>2022NE0002183</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>7/2020</t>
+          <t>13/2017</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3480,7 +3480,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>15023.72</v>
+        <v>35753.5</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3489,19 +3489,19 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em manter o cadastro dos servidores e folha de pagamento pessoal, processar folhas de pagamento e fornecer relatórios para efetivação de pagamento.</t>
+          <t>Contratação de empresa especializada em serviços de acesso a rede de internet, estabelecendo comunicação a partir de circuito de dados existentes entre a contratante e a contratada.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2022NE0002182</t>
+          <t>2022NE0002185</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>8/2020</t>
+          <t>16/2018</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3510,7 +3510,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>2335.68</v>
+        <v>4919.38</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3519,19 +3519,19 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Contratação de Serviço de execução de sistema de protocolo em plataforma web, objetivando o controle e acompanhamento o controle e acompanhamento do registro de todos os documentos ou processos do cli</t>
+          <t>CONTRATAÇÃO DE SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB PARA PUBLICAÇÃO DE INFORMAÇÕES, NOTÍCIAS, VÍDEO E IMAGENS VIA WEBSITE.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2022NE0002185</t>
+          <t>2022NE0002182</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>16/2018</t>
+          <t>8/2020</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3540,7 +3540,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>4919.38</v>
+        <v>2335.68</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3549,19 +3549,19 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB PARA PUBLICAÇÃO DE INFORMAÇÕES, NOTÍCIAS, VÍDEO E IMAGENS VIA WEBSITE.</t>
+          <t>Contratação de Serviço de execução de sistema de protocolo em plataforma web, objetivando o controle e acompanhamento o controle e acompanhamento do registro de todos os documentos ou processos do cli</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2022NE0002183</t>
+          <t>2022NE0002181</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>13/2017</t>
+          <t>7/2020</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3570,7 +3570,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>35753.5</v>
+        <v>15023.72</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3579,19 +3579,19 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviços de acesso a rede de internet, estabelecendo comunicação a partir de circuito de dados existentes entre a contratante e a contratada.</t>
+          <t>Contratação de empresa especializada em manter o cadastro dos servidores e folha de pagamento pessoal, processar folhas de pagamento e fornecer relatórios para efetivação de pagamento.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2025NE0000805</t>
+          <t>2025NE0000808</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>1/2024</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3600,7 +3600,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>25379.97</v>
+        <v>5665.78</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -3609,19 +3609,19 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de empresa especializada em serviço de acesso à rede de internet, para atender as necessidades do Instituto de Desenvolvimento Agropecuário e Florestal Sustentável do Estado do Amazonas – </t>
+          <t>Contratação de empresa especializada na prestação dos serviços de fornecimento de licença de uso de sistema de informação, disponibilizando o Gestor de Conteúdo Web para publicação de informações, not</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2025NE00805</t>
+          <t>2025NE0000807</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>6/2025</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3630,7 +3630,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>25379.97</v>
+        <v>17149.2</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3639,19 +3639,19 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE ACESSO À INTERNET E TRANSMISSÃO DE DADOS REFERENTE AO 2º TA AO CONTRATO 011/2023.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de execução e manutenção de sistema de Recursos Humanos (RH), para atender as necessidades do IDAM, pelo período de 12 (doze) meses</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2025NE0000806</t>
+          <t>2025NE0000804</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>5/2025</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3660,7 +3660,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>2748.84</v>
+        <v>24097.98</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3669,19 +3669,19 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de execução de sistema de protocolo web visando atender às necessidades do IDAM central.</t>
+          <t xml:space="preserve">Contratação de empresa especializada em serviço de acesso à rede de internet, para atender as necessidades do Instituto de Desenvolvimento Agropecuário e Florestal Sustentável do Estado do Amazonas – </t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2025NE0000804</t>
+          <t>2025NE0000806</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>5/2025</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3690,7 +3690,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>24097.98</v>
+        <v>2748.84</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3699,19 +3699,19 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de empresa especializada em serviço de acesso à rede de internet, para atender as necessidades do Instituto de Desenvolvimento Agropecuário e Florestal Sustentável do Estado do Amazonas – </t>
+          <t>Contratação de empresa especializada na prestação de serviços de execução de sistema de protocolo web visando atender às necessidades do IDAM central.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2025NE0000807</t>
+          <t>2025NE00805</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>6/2025</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3720,7 +3720,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>17149.2</v>
+        <v>25379.97</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3729,19 +3729,19 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de execução e manutenção de sistema de Recursos Humanos (RH), para atender as necessidades do IDAM, pelo período de 12 (doze) meses</t>
+          <t>SERVIÇOS DE ACESSO À INTERNET E TRANSMISSÃO DE DADOS REFERENTE AO 2º TA AO CONTRATO 011/2023.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2025NE0000808</t>
+          <t>2025NE0000805</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>1/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3750,7 +3750,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>5665.78</v>
+        <v>25379.97</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -3759,14 +3759,14 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação dos serviços de fornecimento de licença de uso de sistema de informação, disponibilizando o Gestor de Conteúdo Web para publicação de informações, not</t>
+          <t xml:space="preserve">Contratação de empresa especializada em serviço de acesso à rede de internet, para atender as necessidades do Instituto de Desenvolvimento Agropecuário e Florestal Sustentável do Estado do Amazonas – </t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2024NE0000787</t>
+          <t>2024NE0000828</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3780,7 +3780,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>6317.91</v>
+        <v>4472.36</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -3789,14 +3789,14 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conta cobrança no valor de R$ 6.317,91 (Seis mil, trezentos e dezessete reais e noventa e um centavos) referente ao mês de Dezembro/2023, contrato: 007/2020, contratada: PRODAM PROCESSAMENTO DE DADOS </t>
+          <t>Conta cobrança no valor de R$ 4.472,36 (Quatro mil quatrocentos e setenta e dois reais e trinta e seis centavos) referente ao mês de Novembro/2023, contrato: 007/2020, contratada: PRODAM - PROCESSAMEN</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2024NE0000827</t>
+          <t>2024NE0000826</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3810,7 +3810,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>4479.79</v>
+        <v>4448.62</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -3819,14 +3819,14 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Conta cobrança no valor de R$ 4.479,79 (Quatro mil, quatrocentos e setenta e nove reais e setenta e nove centavos) referente ao mês de Outubro/2023, contrato: 007/2020, contratada: PRODAM - PROCESSAME</t>
+          <t>Despesa com cobertura contratual - Serviço de folha de pagamento, referente ao mês 09/2023 - Contrato 7/2020 AD 3, vigência 03/03/2023 a 02/03/2024.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2024NE0000826</t>
+          <t>2024NE0000827</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3840,7 +3840,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>4448.62</v>
+        <v>4479.79</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -3849,14 +3849,14 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Despesa com cobertura contratual - Serviço de folha de pagamento, referente ao mês 09/2023 - Contrato 7/2020 AD 3, vigência 03/03/2023 a 02/03/2024.</t>
+          <t>Conta cobrança no valor de R$ 4.479,79 (Quatro mil, quatrocentos e setenta e nove reais e setenta e nove centavos) referente ao mês de Outubro/2023, contrato: 007/2020, contratada: PRODAM - PROCESSAME</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2024NE0000828</t>
+          <t>2024NE0000787</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3870,7 +3870,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>4472.36</v>
+        <v>6317.91</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -3879,14 +3879,14 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Conta cobrança no valor de R$ 4.472,36 (Quatro mil quatrocentos e setenta e dois reais e trinta e seis centavos) referente ao mês de Novembro/2023, contrato: 007/2020, contratada: PRODAM - PROCESSAMEN</t>
+          <t xml:space="preserve">Conta cobrança no valor de R$ 6.317,91 (Seis mil, trezentos e dezessete reais e noventa e um centavos) referente ao mês de Dezembro/2023, contrato: 007/2020, contratada: PRODAM PROCESSAMENTO DE DADOS </t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2019NE00417</t>
+          <t>2019NE00418</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -3896,7 +3896,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>3171.62</v>
+        <v>795.22</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -3905,14 +3905,14 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DO SALDO DO EMPENHO Nº 009/2019, EM VIRTUDE DE UM NOVO TERMO ADITIVO FIRMADO.</t>
+          <t>ANULAÇÃO TOTAL DO SALDO DO EMPENHO Nº 030/2019, EM VIRTUDE DE UM NOVO TERMO ADITIVO FIRMADO.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2019NE00418</t>
+          <t>2019NE00417</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>795.22</v>
+        <v>3171.62</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -3931,24 +3931,28 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DO SALDO DO EMPENHO Nº 030/2019, EM VIRTUDE DE UM NOVO TERMO ADITIVO FIRMADO.</t>
+          <t>ANULAÇÃO TOTAL DO SALDO DO EMPENHO Nº 009/2019, EM VIRTUDE DE UM NOVO TERMO ADITIVO FIRMADO.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2018NE00756</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr"/>
+          <t>2018NE00754</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>13/2017</t>
+        </is>
+      </c>
       <c r="C119" t="inlineStr">
         <is>
           <t>24/05/2018</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>40215.84</v>
+        <v>31288.16</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -3957,28 +3961,24 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>-REFERENTE A UM TERMO DE CONTRATO A SER FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS-IDAM E A EMPRESA: PRODAM PROCESSAMENTO DE DADOS AMAZONAS</t>
+          <t>-REFERENTE AO PRIMEIRO TERMO ADITIVO AO CONTRATO Nº 013/2017 FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS - IDAM E A EMPRESA: PRODAM PROCESSA</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2018NE00754</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>13/2017</t>
-        </is>
-      </c>
+          <t>2018NE00756</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
           <t>24/05/2018</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>31288.16</v>
+        <v>40215.84</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -3987,19 +3987,19 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>-REFERENTE AO PRIMEIRO TERMO ADITIVO AO CONTRATO Nº 013/2017 FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS - IDAM E A EMPRESA: PRODAM PROCESSA</t>
+          <t>-REFERENTE A UM TERMO DE CONTRATO A SER FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS-IDAM E A EMPRESA: PRODAM PROCESSAMENTO DE DADOS AMAZONAS</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2016NE01782</t>
+          <t>2016NE01783</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>14/2013</t>
+          <t>4/2015</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4008,7 +4008,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>6120</v>
+        <v>4517.98</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4017,19 +4017,19 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>-REFERENTE A PARTE DO TERCEIRO TERMO ADITIVO AO TERMO DE CONTRATO Nº 014/2013, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS-IDAM E A EMPRESA:</t>
+          <t>-REFERENTE A PARTE DO PRIMEIRO TERMO ADITIVO AO TERMO DE CONTRATO Nº 004/2015, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS - IDAM E A EMPRES</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2016NE01783</t>
+          <t>2016NE01782</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>4/2015</t>
+          <t>14/2013</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4038,7 +4038,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>4517.98</v>
+        <v>6120</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4047,19 +4047,19 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>-REFERENTE A PARTE DO PRIMEIRO TERMO ADITIVO AO TERMO DE CONTRATO Nº 004/2015, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS - IDAM E A EMPRES</t>
+          <t>-REFERENTE A PARTE DO TERCEIRO TERMO ADITIVO AO TERMO DE CONTRATO Nº 014/2013, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS-IDAM E A EMPRESA:</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2015NE01593</t>
+          <t>2015NE01591</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>14/2013</t>
+          <t>17/2014</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4068,7 +4068,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>6186.3</v>
+        <v>3000</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4077,14 +4077,14 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Cobertura Financeira 2015</t>
+          <t>-ANULAÇÃO QUE SE FAZ DA NOTA DE EMPENHO Nº 27/2015, POR MOTIVO DO TERMINO DA VIGENCIA DO REFERIDO CONTRATO.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2015NE01596</t>
+          <t>2015NE01598</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">-REFERENTE À PARTE DO PRIMEIRO TERMO ADITIVO AO TERMO DE CONTRATO Nº 017/2014 FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS-IDAM E A EMPRESA: </t>
+          <t>Cobertura Financeira 2015</t>
         </is>
       </c>
     </row>
@@ -4144,7 +4144,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2015NE01598</t>
+          <t>2015NE01596</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4167,19 +4167,19 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Cobertura Financeira 2015</t>
+          <t xml:space="preserve">-REFERENTE À PARTE DO PRIMEIRO TERMO ADITIVO AO TERMO DE CONTRATO Nº 017/2014 FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS-IDAM E A EMPRESA: </t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2015NE01591</t>
+          <t>2015NE01593</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>17/2014</t>
+          <t>14/2013</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4188,7 +4188,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>3000</v>
+        <v>6186.3</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>-ANULAÇÃO QUE SE FAZ DA NOTA DE EMPENHO Nº 27/2015, POR MOTIVO DO TERMINO DA VIGENCIA DO REFERIDO CONTRATO.</t>
+          <t>Cobertura Financeira 2015</t>
         </is>
       </c>
     </row>
@@ -4264,17 +4264,21 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2016NE01774</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr"/>
+          <t>2016NE01775</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>14/2013</t>
+        </is>
+      </c>
       <c r="C130" t="inlineStr">
         <is>
           <t>22/12/2016</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>3366.3</v>
+        <v>1632</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4283,28 +4287,24 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>-ANULAÇÃO QUE SE FAZ DO SALDO DA NOTA DE EMPENHO Nº 1332/2016, EM VIRTUDE DO ENCERRAMENTO DO EXERCÍCIO DE 2016.</t>
+          <t>-REFERENTE A PARTE DO TERCEIRO TERMO ADITIVO AO TERMO DE CONTRATO Nº 014/2013, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS-IDAM E A EMPRESA:</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2016NE01775</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>14/2013</t>
-        </is>
-      </c>
+          <t>2016NE01774</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
         <is>
           <t>22/12/2016</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1632</v>
+        <v>3366.3</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4313,14 +4313,14 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>-REFERENTE A PARTE DO TERCEIRO TERMO ADITIVO AO TERMO DE CONTRATO Nº 014/2013, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS-IDAM E A EMPRESA:</t>
+          <t>-ANULAÇÃO QUE SE FAZ DO SALDO DA NOTA DE EMPENHO Nº 1332/2016, EM VIRTUDE DO ENCERRAMENTO DO EXERCÍCIO DE 2016.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2015NE02347</t>
+          <t>2015NE02354</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
@@ -4330,7 +4330,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1535.31</v>
+        <v>3000</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2015NE02341</t>
+          <t>2015NE02344</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
@@ -4356,7 +4356,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>84</v>
+        <v>1651.87</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2015NE02346</t>
+          <t>2015NE02348</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -4382,7 +4382,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>8232.35</v>
+        <v>38568.09</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2015NE02353</t>
+          <t>2015NE02342</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>4542.64</v>
+        <v>6000</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2015NE02342</t>
+          <t>2015NE02353</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
@@ -4434,7 +4434,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>6000</v>
+        <v>4542.64</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -4450,7 +4450,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2015NE02348</t>
+          <t>2015NE02346</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
@@ -4460,7 +4460,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>38568.09</v>
+        <v>8232.35</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2015NE02344</t>
+          <t>2015NE02341</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
@@ -4486,7 +4486,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1651.87</v>
+        <v>84</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2015NE02354</t>
+          <t>2015NE02347</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
@@ -4512,7 +4512,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>3000</v>
+        <v>1535.31</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -4528,12 +4528,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2024NE0001503</t>
+          <t>2024NE0001501</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>8/2020</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4542,7 +4542,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>2473.48</v>
+        <v>48195.96</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -4551,19 +4551,19 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Contratação de Serviço de execução de sistema de protocolo em plataforma web, objetivando o controle e acompanhamento o controle e acompanhamento do registro de todos os documentos ou processos do cli</t>
+          <t xml:space="preserve">Contratação de empresa especializada em serviço de acesso à rede de internet, para atender as necessidades do Instituto de Desenvolvimento Agropecuário e Florestal Sustentável do Estado do Amazonas – </t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2024NE0001504</t>
+          <t>2024NE0001502</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>7/2020</t>
+          <t>1/2024</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4572,7 +4572,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>12635.82</v>
+        <v>5435.32</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -4581,19 +4581,19 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em manter o cadastro dos servidores e folha de pagamento pessoal, processar folhas de pagamento e fornecer relatórios para efetivação de pagamento. TC: 0007/2020 A</t>
+          <t>Contratação de empresa especializada na prestação dos serviços de fornecimento de licença de uso de sistema de informação, disponibilizando o Gestor de Conteúdo Web para publicação de informações, not</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2024NE0001502</t>
+          <t>2024NE0001504</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>1/2024</t>
+          <t>7/2020</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4602,7 +4602,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>5435.32</v>
+        <v>12635.82</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -4611,19 +4611,19 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação dos serviços de fornecimento de licença de uso de sistema de informação, disponibilizando o Gestor de Conteúdo Web para publicação de informações, not</t>
+          <t>Contratação de empresa especializada em manter o cadastro dos servidores e folha de pagamento pessoal, processar folhas de pagamento e fornecer relatórios para efetivação de pagamento. TC: 0007/2020 A</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2024NE0001501</t>
+          <t>2024NE0001503</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>8/2020</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4632,7 +4632,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>48195.96</v>
+        <v>2473.48</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de empresa especializada em serviço de acesso à rede de internet, para atender as necessidades do Instituto de Desenvolvimento Agropecuário e Florestal Sustentável do Estado do Amazonas – </t>
+          <t>Contratação de Serviço de execução de sistema de protocolo em plataforma web, objetivando o controle e acompanhamento o controle e acompanhamento do registro de todos os documentos ou processos do cli</t>
         </is>
       </c>
     </row>
@@ -4674,14 +4674,10 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2024NE0000014</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>11/2023</t>
-        </is>
-      </c>
+          <t>2024NE0000017</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr">
         <is>
           <t>22/01/2024</t>
@@ -4697,17 +4693,21 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de empresa especializada em serviço de acesso à rede de internet, para atender as necessidades do Instituto de Desenvolvimento Agropecuário e Florestal Sustentável do Estado do Amazonas – </t>
+          <t>ANULAÇÃO DA 2024NE0000014 para correção da descrição</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2024NE0000017</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr"/>
+          <t>2024NE0000014</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>11/2023</t>
+        </is>
+      </c>
       <c r="C146" t="inlineStr">
         <is>
           <t>22/01/2024</t>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DA 2024NE0000014 para correção da descrição</t>
+          <t xml:space="preserve">Contratação de empresa especializada em serviço de acesso à rede de internet, para atender as necessidades do Instituto de Desenvolvimento Agropecuário e Florestal Sustentável do Estado do Amazonas – </t>
         </is>
       </c>
     </row>
@@ -4760,12 +4760,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2016NE00097</t>
+          <t>2016NE00098</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>4/2015</t>
+          <t>3/2015</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -4774,7 +4774,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>22589.9</v>
+        <v>9027.75</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -4783,19 +4783,19 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>-REFERENTE A PARTE DO PRIMEIRO TERMO ADITIVO AO TERMO DE CONTRATO Nº 004/2015, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS - IDAM E A EMPRES</t>
+          <t>-REFERENTE A PARTE DO PRIMEIRO TERMO ADITIVO AO TERMO DE CONTRATO DE Nº 003/2015, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS - IDAM E A EMP</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2016NE00098</t>
+          <t>2016NE00097</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>3/2015</t>
+          <t>4/2015</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -4804,7 +4804,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>9027.75</v>
+        <v>22589.9</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -4813,14 +4813,14 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>-REFERENTE A PARTE DO PRIMEIRO TERMO ADITIVO AO TERMO DE CONTRATO DE Nº 003/2015, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS - IDAM E A EMP</t>
+          <t>-REFERENTE A PARTE DO PRIMEIRO TERMO ADITIVO AO TERMO DE CONTRATO Nº 004/2015, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS - IDAM E A EMPRES</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2015NE01781</t>
+          <t>2015NE01779</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4876,7 +4876,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2015NE01779</t>
+          <t>2015NE01781</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4966,7 +4966,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2017NE00115</t>
+          <t>2017NE00111</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -5022,7 +5022,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2017NE00111</t>
+          <t>2017NE00115</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -5082,21 +5082,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2020NE00419</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>13/2017</t>
-        </is>
-      </c>
+          <t>2020NE00416</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr"/>
       <c r="C159" t="inlineStr">
         <is>
           <t>20/05/2020</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>16937.82</v>
+        <v>1106.57</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -5105,14 +5101,14 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviços de acesso a rede de internet, estabelecendo comunicação a partir de circuito de dados existentes entre a contratante e a contratada.</t>
+          <t>Anulação total que se faz da NE nº 008/2020, em virtude do termino do Contrato nº 003/2015.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2020NE00415</t>
+          <t>2020NE00418</t>
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
@@ -5122,7 +5118,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>3439.24</v>
+        <v>15.61</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -5131,7 +5127,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Anulação total que se faz da NE nº 007/2020, em virtude do termino do Contrato nº 004/2015.</t>
+          <t>Anulação parcial da NE nº 099/2020, para ser utilizado na complementação orçamentária da Renovação do Termo de contrato nº 13/2017, por mais doze meses.</t>
         </is>
       </c>
     </row>
@@ -5164,7 +5160,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2020NE00418</t>
+          <t>2020NE00415</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
@@ -5174,7 +5170,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>15.61</v>
+        <v>3439.24</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -5183,24 +5179,28 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Anulação parcial da NE nº 099/2020, para ser utilizado na complementação orçamentária da Renovação do Termo de contrato nº 13/2017, por mais doze meses.</t>
+          <t>Anulação total que se faz da NE nº 007/2020, em virtude do termino do Contrato nº 004/2015.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2020NE00416</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr"/>
+          <t>2020NE00419</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>13/2017</t>
+        </is>
+      </c>
       <c r="C163" t="inlineStr">
         <is>
           <t>20/05/2020</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1106.57</v>
+        <v>16937.82</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Anulação total que se faz da NE nº 008/2020, em virtude do termino do Contrato nº 003/2015.</t>
+          <t>Contratação de empresa especializada em serviços de acesso a rede de internet, estabelecendo comunicação a partir de circuito de dados existentes entre a contratante e a contratada.</t>
         </is>
       </c>
     </row>
@@ -5246,7 +5246,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2024NE0001786</t>
+          <t>2024NE0001784</t>
         </is>
       </c>
       <c r="B165" t="inlineStr"/>
@@ -5256,7 +5256,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>3044.29</v>
+        <v>1236.74</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -5265,14 +5265,14 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Anulação do Saldo da 2024NE0001504, em atendimento ao Decreto nº 50.522/2024 datado de 22.10.2024, de Encerramento da Execução Orçamentária, Financeira e Contábil do Exercício 2024.</t>
+          <t>Anulação do Saldo da 2024NE0001503, em atendimento ao Decreto nº 50.522/2024 datado de 22.10.2024, de Encerramento da Execução Orçamentária, Financeira e Contábil do Exercício 2024.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2024NE0001783</t>
+          <t>2024NE0001782</t>
         </is>
       </c>
       <c r="B166" t="inlineStr"/>
@@ -5282,7 +5282,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>24097.98</v>
+        <v>3362.46</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -5291,14 +5291,14 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Anulação do Saldo da 2024NE0001501, em atendimento ao Decreto nº 50.522/2024 datado de 22.10.2024, de Encerramento da Execução Orçamentária, Financeira e Contábil do Exercício 2024.</t>
+          <t>Anulação do Saldo da 2024NE0000013, em atendimento ao Decreto nº 50.522/2024 datado de 22.10.2024, de Encerramento da Execução Orçamentária, Financeira e Contábil do Exercício 2024.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2024NE0001782</t>
+          <t>2024NE0001783</t>
         </is>
       </c>
       <c r="B167" t="inlineStr"/>
@@ -5308,7 +5308,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>3362.46</v>
+        <v>24097.98</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -5317,14 +5317,14 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Anulação do Saldo da 2024NE0000013, em atendimento ao Decreto nº 50.522/2024 datado de 22.10.2024, de Encerramento da Execução Orçamentária, Financeira e Contábil do Exercício 2024.</t>
+          <t>Anulação do Saldo da 2024NE0001501, em atendimento ao Decreto nº 50.522/2024 datado de 22.10.2024, de Encerramento da Execução Orçamentária, Financeira e Contábil do Exercício 2024.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2024NE0001784</t>
+          <t>2024NE0001786</t>
         </is>
       </c>
       <c r="B168" t="inlineStr"/>
@@ -5334,7 +5334,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>1236.74</v>
+        <v>3044.29</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Anulação do Saldo da 2024NE0001503, em atendimento ao Decreto nº 50.522/2024 datado de 22.10.2024, de Encerramento da Execução Orçamentária, Financeira e Contábil do Exercício 2024.</t>
+          <t>Anulação do Saldo da 2024NE0001504, em atendimento ao Decreto nº 50.522/2024 datado de 22.10.2024, de Encerramento da Execução Orçamentária, Financeira e Contábil do Exercício 2024.</t>
         </is>
       </c>
     </row>
@@ -5436,12 +5436,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2020NE00099</t>
+          <t>2020NE00100</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>8/2020</t>
+          <t>7/2020</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5450,7 +5450,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>21431.8</v>
+        <v>49557.7</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -5459,19 +5459,19 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Serviço de execução de sistema de protocolo em plataforma web, objetivando o controle e acompanhamento o controle e acompanhamento do registro de todos os documentos ou processos do cliente para atend</t>
+          <t>contratação de empresa especializada em manter o cadastro dos servidores e folha de pagamento pessoal, processar folhas de pagamento e fornecer relatórios para efetivação de pagamento.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2020NE00100</t>
+          <t>2020NE00099</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>7/2020</t>
+          <t>8/2020</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5480,7 +5480,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>49557.7</v>
+        <v>21431.8</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -5489,14 +5489,14 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>contratação de empresa especializada em manter o cadastro dos servidores e folha de pagamento pessoal, processar folhas de pagamento e fornecer relatórios para efetivação de pagamento.</t>
+          <t>Serviço de execução de sistema de protocolo em plataforma web, objetivando o controle e acompanhamento o controle e acompanhamento do registro de todos os documentos ou processos do cliente para atend</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2015NE00185</t>
+          <t>2015NE00191</t>
         </is>
       </c>
       <c r="B174" t="inlineStr"/>
@@ -5506,7 +5506,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>1351.86</v>
+        <v>6194.51</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2015NE00187</t>
+          <t>2015NE00172</t>
         </is>
       </c>
       <c r="B175" t="inlineStr"/>
@@ -5532,7 +5532,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>6157.18</v>
+        <v>1500</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2015NE00184</t>
+          <t>2015NE00186</t>
         </is>
       </c>
       <c r="B176" t="inlineStr"/>
@@ -5558,7 +5558,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>1414.26</v>
+        <v>2587.79</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -5574,7 +5574,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2015NE00189</t>
+          <t>2015NE00193</t>
         </is>
       </c>
       <c r="B177" t="inlineStr"/>
@@ -5584,7 +5584,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>6157.18</v>
+        <v>6194.51</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2015NE00190</t>
+          <t>2015NE00188</t>
         </is>
       </c>
       <c r="B178" t="inlineStr"/>
@@ -5610,7 +5610,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>1445.36</v>
+        <v>6157.18</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2015NE00173</t>
+          <t>2015NE00174</t>
         </is>
       </c>
       <c r="B179" t="inlineStr"/>
@@ -5678,7 +5678,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2015NE00174</t>
+          <t>2015NE00173</t>
         </is>
       </c>
       <c r="B181" t="inlineStr"/>
@@ -5704,7 +5704,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2015NE00188</t>
+          <t>2015NE00190</t>
         </is>
       </c>
       <c r="B182" t="inlineStr"/>
@@ -5714,7 +5714,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>6157.18</v>
+        <v>1445.36</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2015NE00193</t>
+          <t>2015NE00189</t>
         </is>
       </c>
       <c r="B183" t="inlineStr"/>
@@ -5740,7 +5740,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>6194.51</v>
+        <v>6157.18</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2015NE00186</t>
+          <t>2015NE00184</t>
         </is>
       </c>
       <c r="B184" t="inlineStr"/>
@@ -5766,7 +5766,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>2587.79</v>
+        <v>1414.26</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2015NE00172</t>
+          <t>2015NE00187</t>
         </is>
       </c>
       <c r="B185" t="inlineStr"/>
@@ -5792,7 +5792,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>1500</v>
+        <v>6157.18</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2015NE00191</t>
+          <t>2015NE00185</t>
         </is>
       </c>
       <c r="B186" t="inlineStr"/>
@@ -5818,7 +5818,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>6194.51</v>
+        <v>1351.86</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -5834,21 +5834,17 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2024NE0000002</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>7/2020</t>
-        </is>
-      </c>
+          <t>2024NE0000012</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr"/>
       <c r="C187" t="inlineStr">
         <is>
           <t>19/01/2024</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>15910.12</v>
+        <v>46688.24</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -5857,28 +5853,24 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em manter o cadastro dos servidores e folha de pagamento pessoal, processar folhas de pagamento e fornecer relatórios para efetivação de pagamento. TC: 0007/2020 A</t>
+          <t>Anulação da 2024NE0000008, para correção da Descrição</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2024NE0000008</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>11/2023</t>
-        </is>
-      </c>
+          <t>2024NE0000009</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr"/>
       <c r="C188" t="inlineStr">
         <is>
           <t>19/01/2024</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>46688.24</v>
+        <v>15910.12</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -5887,24 +5879,28 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de empresa especializada em serviço de acesso à rede de internet, para atender as necessidades do Instituto de Desenvolvimento Agropecuário e Florestal Sustentável do Estado do Amazonas – </t>
+          <t>Anulação da 2024NE0000002, para correção da Descrição</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2024NE0000009</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr"/>
+          <t>2024NE0000008</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>11/2023</t>
+        </is>
+      </c>
       <c r="C189" t="inlineStr">
         <is>
           <t>19/01/2024</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>15910.12</v>
+        <v>46688.24</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -5913,24 +5909,28 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Anulação da 2024NE0000002, para correção da Descrição</t>
+          <t xml:space="preserve">Contratação de empresa especializada em serviço de acesso à rede de internet, para atender as necessidades do Instituto de Desenvolvimento Agropecuário e Florestal Sustentável do Estado do Amazonas – </t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2024NE0000012</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr"/>
+          <t>2024NE0000002</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>7/2020</t>
+        </is>
+      </c>
       <c r="C190" t="inlineStr">
         <is>
           <t>19/01/2024</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>46688.24</v>
+        <v>15910.12</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -5939,19 +5939,19 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Anulação da 2024NE0000008, para correção da Descrição</t>
+          <t>Contratação de empresa especializada em manter o cadastro dos servidores e folha de pagamento pessoal, processar folhas de pagamento e fornecer relatórios para efetivação de pagamento. TC: 0007/2020 A</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2022NE0002857</t>
+          <t>2022NE0002858</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>13/2017</t>
+          <t>16/2018</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -5960,7 +5960,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>17876.75</v>
+        <v>2459.69</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -5969,19 +5969,19 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviços de acesso a rede de internet, estabelecendo comunicação a partir de circuito de dados existentes entre a contratante e a contratada.</t>
+          <t>CONTRATAÇÃO DE SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB PARA PUBLICAÇÃO DE INFORMAÇÕES, NOTÍCIAS, VÍDEO E IMAGENS VIA WEBSITE.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2022NE0002856</t>
+          <t>2022NE0002855</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>8/2020</t>
+          <t>7/2020</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -5990,7 +5990,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>1167.84</v>
+        <v>7511.86</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -5999,19 +5999,19 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Contratação de Serviço de execução de sistema de protocolo em plataforma web, objetivando o controle e acompanhamento o controle e acompanhamento do registro de todos os documentos ou processos do cli</t>
+          <t>Contratação de empresa especializada em manter o cadastro dos servidores e folha de pagamento pessoal, processar folhas de pagamento e fornecer relatórios para efetivação de pagamento.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2022NE0002855</t>
+          <t>2022NE0002856</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>7/2020</t>
+          <t>8/2020</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -6020,7 +6020,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>7511.86</v>
+        <v>1167.84</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -6029,19 +6029,19 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em manter o cadastro dos servidores e folha de pagamento pessoal, processar folhas de pagamento e fornecer relatórios para efetivação de pagamento.</t>
+          <t>Contratação de Serviço de execução de sistema de protocolo em plataforma web, objetivando o controle e acompanhamento o controle e acompanhamento do registro de todos os documentos ou processos do cli</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2022NE0002858</t>
+          <t>2022NE0002857</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>16/2018</t>
+          <t>13/2017</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -6050,7 +6050,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>2459.69</v>
+        <v>17876.75</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB PARA PUBLICAÇÃO DE INFORMAÇÕES, NOTÍCIAS, VÍDEO E IMAGENS VIA WEBSITE.</t>
+          <t>Contratação de empresa especializada em serviços de acesso a rede de internet, estabelecendo comunicação a partir de circuito de dados existentes entre a contratante e a contratada.</t>
         </is>
       </c>
     </row>
@@ -6126,12 +6126,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2021NE0001331</t>
+          <t>2021NE0001342</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>13/2017</t>
+          <t>8/2020</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -6140,7 +6140,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>71507</v>
+        <v>10674.76</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -6149,7 +6149,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviços de acesso a rede de internet, estabelecendo comunicação a partir de circuito de dados existentes entre a contratante e a contratada.</t>
+          <t>Serviço de execução de sistema de protocolo em plataforma web, objetivando o controle e acompanhamento o controle e acompanhamento do registro de todos os documentos ou processos do cliente para atend</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2021NE0001342</t>
+          <t>2021NE0001331</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>8/2020</t>
+          <t>13/2017</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -6200,7 +6200,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>10674.76</v>
+        <v>71507</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Serviço de execução de sistema de protocolo em plataforma web, objetivando o controle e acompanhamento o controle e acompanhamento do registro de todos os documentos ou processos do cliente para atend</t>
+          <t>Contratação de empresa especializada em serviços de acesso a rede de internet, estabelecendo comunicação a partir de circuito de dados existentes entre a contratante e a contratada.</t>
         </is>
       </c>
     </row>
@@ -6276,12 +6276,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2022NE0000853</t>
+          <t>2022NE0000851</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>13/2017</t>
+          <t>8/2020</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -6290,7 +6290,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>17876.75</v>
+        <v>4671.36</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -6299,19 +6299,19 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviços de acesso a rede de internet, estabelecendo comunicação a partir de circuito de dados existentes entre a contratante e a contratada.</t>
+          <t>Contratação de Serviço de execução de sistema de protocolo em plataforma web, objetivando o controle e acompanhamento o controle e acompanhamento do registro de todos os documentos ou processos do cli</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2022NE0000850</t>
+          <t>2022NE0000854</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>7/2020</t>
+          <t>16/2018</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -6320,7 +6320,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>30047.44</v>
+        <v>9838.76</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -6329,19 +6329,19 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em manter o cadastro dos servidores e folha de pagamento pessoal, processar folhas de pagamento e fornecer relatórios para efetivação de pagamento.</t>
+          <t>CONTRATAÇÃO DE SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB PARA PUBLICAÇÃO DE INFORMAÇÕES, NOTÍCIAS, VÍDEO E IMAGENS VIA WEBSITE.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2022NE0000854</t>
+          <t>2022NE0000850</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>16/2018</t>
+          <t>7/2020</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -6350,7 +6350,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>9838.76</v>
+        <v>30047.44</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -6359,19 +6359,19 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB PARA PUBLICAÇÃO DE INFORMAÇÕES, NOTÍCIAS, VÍDEO E IMAGENS VIA WEBSITE.</t>
+          <t>Contratação de empresa especializada em manter o cadastro dos servidores e folha de pagamento pessoal, processar folhas de pagamento e fornecer relatórios para efetivação de pagamento.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2022NE0000851</t>
+          <t>2022NE0000853</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>8/2020</t>
+          <t>13/2017</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -6380,7 +6380,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>4671.36</v>
+        <v>17876.75</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -6389,19 +6389,19 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Contratação de Serviço de execução de sistema de protocolo em plataforma web, objetivando o controle e acompanhamento o controle e acompanhamento do registro de todos os documentos ou processos do cli</t>
+          <t>Contratação de empresa especializada em serviços de acesso a rede de internet, estabelecendo comunicação a partir de circuito de dados existentes entre a contratante e a contratada.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2020NE00534</t>
+          <t>2020NE00535</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>7/2020</t>
+          <t>8/2020</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>1627.51</v>
+        <v>1224.31</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -6419,19 +6419,19 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>VIRTUDE DO SERVIÇO DE EXECUÇÃO DO SISTEMA DE RECURSOS HUMANOS E FOLHA DE PAGAMENTO POR CONTRA CHEQUE GERADO EM MÍDIA ELETRÔNICA, ESTÁ SEM COBERTURA CONTRATUAL NO PERÍODO DE 01 A 28 DE FEVEREIRO DE 202</t>
+          <t>EM VIRTUDE DO SERVIÇO DE EXECUÇÃO DO SISTEMA DE PROTOCOLO WEB ESTÁ SEM COBERTURA CONTRATUAL NO PERÍODO DE 01 A 28 DE FEVEREIRO DE 2020. NF Nº 13472 EMITIDA EM 28/02/2020, PARECER DE Nº 056/2020 - PJ/I</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2020NE00535</t>
+          <t>2020NE00534</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>8/2020</t>
+          <t>7/2020</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -6440,7 +6440,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>1224.31</v>
+        <v>1627.51</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -6449,14 +6449,14 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>EM VIRTUDE DO SERVIÇO DE EXECUÇÃO DO SISTEMA DE PROTOCOLO WEB ESTÁ SEM COBERTURA CONTRATUAL NO PERÍODO DE 01 A 28 DE FEVEREIRO DE 2020. NF Nº 13472 EMITIDA EM 28/02/2020, PARECER DE Nº 056/2020 - PJ/I</t>
+          <t>VIRTUDE DO SERVIÇO DE EXECUÇÃO DO SISTEMA DE RECURSOS HUMANOS E FOLHA DE PAGAMENTO POR CONTRA CHEQUE GERADO EM MÍDIA ELETRÔNICA, ESTÁ SEM COBERTURA CONTRATUAL NO PERÍODO DE 01 A 28 DE FEVEREIRO DE 202</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2016NE01755</t>
+          <t>2016NE01756</t>
         </is>
       </c>
       <c r="B208" t="inlineStr"/>
@@ -6466,7 +6466,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>628.99</v>
+        <v>932.25</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -6475,14 +6475,14 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>-ANULAÇÃO DO SALDO DA NOTA DE EMPENHO N.º 001343/2016, EM VIRTUDE DO ENCERRAMENTO DO EXERCÍCIO DE 2016.</t>
+          <t>-ANULAÇÃO DO SALDO DA NOTA DE EMPENHO N.º 001590/2016, EM VIRTUDE DO ENCERRAMENTO DO EXERCÍCIO DE 2016.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2016NE01753</t>
+          <t>2016NE01752</t>
         </is>
       </c>
       <c r="B209" t="inlineStr"/>
@@ -6492,7 +6492,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>573.4299999999999</v>
+        <v>925.47</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>-ANULAÇÃO DO SALDO DA NOTA DE EMPENHO N.º 0098/2016, EM VIRTUDE DO ENCERRAMENTO DO EXERCÍCIO DE 2016.</t>
+          <t>-ANULAÇÃO DO SALDO DA NOTA DE EMPENHO N.º 0097/2016, EM VIRTUDE DO ENCERRAMENTO DO EXERCÍCIO DE 2016.</t>
         </is>
       </c>
     </row>
@@ -6534,7 +6534,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2016NE01752</t>
+          <t>2016NE01753</t>
         </is>
       </c>
       <c r="B211" t="inlineStr"/>
@@ -6544,7 +6544,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>925.47</v>
+        <v>573.4299999999999</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -6553,14 +6553,14 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>-ANULAÇÃO DO SALDO DA NOTA DE EMPENHO N.º 0097/2016, EM VIRTUDE DO ENCERRAMENTO DO EXERCÍCIO DE 2016.</t>
+          <t>-ANULAÇÃO DO SALDO DA NOTA DE EMPENHO N.º 0098/2016, EM VIRTUDE DO ENCERRAMENTO DO EXERCÍCIO DE 2016.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2016NE01756</t>
+          <t>2016NE01755</t>
         </is>
       </c>
       <c r="B212" t="inlineStr"/>
@@ -6570,7 +6570,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>932.25</v>
+        <v>628.99</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
@@ -6579,14 +6579,14 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>-ANULAÇÃO DO SALDO DA NOTA DE EMPENHO N.º 001590/2016, EM VIRTUDE DO ENCERRAMENTO DO EXERCÍCIO DE 2016.</t>
+          <t>-ANULAÇÃO DO SALDO DA NOTA DE EMPENHO N.º 001343/2016, EM VIRTUDE DO ENCERRAMENTO DO EXERCÍCIO DE 2016.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2025NE0001314</t>
+          <t>2025NE0001317</t>
         </is>
       </c>
       <c r="B213" t="inlineStr"/>
@@ -6596,7 +6596,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>1726.11</v>
+        <v>2670.98</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -6605,14 +6605,14 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>PARA ANULAÇÃO PARCIAL DO EMPENHO 2/2025.</t>
+          <t>PARA ANULAÇÃO PARCIAL DO EMPENHO 431/2025.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2025NE0001315</t>
+          <t>2025NE0001316</t>
         </is>
       </c>
       <c r="B214" t="inlineStr"/>
@@ -6622,7 +6622,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>2670.98</v>
+        <v>17900.93</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -6631,14 +6631,14 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>PARA ANULAÇÃO PARCIAL DO EMPENHO 288/2025.</t>
+          <t>PARA ANULAÇÃO PARCIAL DO EMPENHO 312/2025.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2025NE0001316</t>
+          <t>2025NE0001315</t>
         </is>
       </c>
       <c r="B215" t="inlineStr"/>
@@ -6648,7 +6648,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>17900.93</v>
+        <v>2670.98</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
@@ -6657,14 +6657,14 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>PARA ANULAÇÃO PARCIAL DO EMPENHO 312/2025.</t>
+          <t>PARA ANULAÇÃO PARCIAL DO EMPENHO 288/2025.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2025NE0001317</t>
+          <t>2025NE0001314</t>
         </is>
       </c>
       <c r="B216" t="inlineStr"/>
@@ -6674,7 +6674,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>2670.98</v>
+        <v>1726.11</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
@@ -6683,19 +6683,19 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>PARA ANULAÇÃO PARCIAL DO EMPENHO 431/2025.</t>
+          <t>PARA ANULAÇÃO PARCIAL DO EMPENHO 2/2025.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2024NE0001247</t>
+          <t>2024NE0001245</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>8/2020</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -6704,7 +6704,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>48195.96</v>
+        <v>2473.48</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -6713,7 +6713,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de empresa especializada em serviço de acesso à rede de internet, para atender as necessidades do Instituto de Desenvolvimento Agropecuário e Florestal Sustentável do Estado do Amazonas – </t>
+          <t>Contratação de Serviço de execução de sistema de protocolo em plataforma web, objetivando o controle e acompanhamento o controle e acompanhamento do registro de todos os documentos ou processos do cli</t>
         </is>
       </c>
     </row>
@@ -6750,12 +6750,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2024NE0001245</t>
+          <t>2024NE0001247</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>8/2020</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -6764,7 +6764,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>2473.48</v>
+        <v>48195.96</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -6773,14 +6773,14 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Contratação de Serviço de execução de sistema de protocolo em plataforma web, objetivando o controle e acompanhamento o controle e acompanhamento do registro de todos os documentos ou processos do cli</t>
+          <t xml:space="preserve">Contratação de empresa especializada em serviço de acesso à rede de internet, para atender as necessidades do Instituto de Desenvolvimento Agropecuário e Florestal Sustentável do Estado do Amazonas – </t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2016NE01235</t>
+          <t>2016NE01234</t>
         </is>
       </c>
       <c r="B220" t="inlineStr"/>
@@ -6790,7 +6790,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>5830.67</v>
+        <v>1100.84</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -6799,7 +6799,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>-ANULAÇÃO TOTAL QUE SE DA NE Nº 063/2016 EMITIDA EM: 04/01/2016, EM VIRTUDE DO TERMINO DA VIGÊNCIA DO CONTRATO ADITIVO.</t>
+          <t>-ANULAÇÃO TOTAL QUE SE DA NE Nº 083/2016 EMITIDA EM: 04/01/2016, EM VIRTUDE DO TERMINO DA VIGÊNCIA DO CONTRATO ADITIVO.</t>
         </is>
       </c>
     </row>
@@ -6836,7 +6836,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2016NE01234</t>
+          <t>2016NE01235</t>
         </is>
       </c>
       <c r="B222" t="inlineStr"/>
@@ -6846,7 +6846,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>1100.84</v>
+        <v>5830.67</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
@@ -6855,19 +6855,19 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>-ANULAÇÃO TOTAL QUE SE DA NE Nº 083/2016 EMITIDA EM: 04/01/2016, EM VIRTUDE DO TERMINO DA VIGÊNCIA DO CONTRATO ADITIVO.</t>
+          <t>-ANULAÇÃO TOTAL QUE SE DA NE Nº 063/2016 EMITIDA EM: 04/01/2016, EM VIRTUDE DO TERMINO DA VIGÊNCIA DO CONTRATO ADITIVO.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2017NE01615</t>
+          <t>2017NE01623</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>13/2017</t>
+          <t>3/2015</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -6876,7 +6876,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>12600</v>
+        <v>1934.28</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
@@ -6885,19 +6885,19 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t xml:space="preserve">-REFERENTE A UM TERMO DE CONTRATO Nº 013/2017 FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS - IDAM E A EMPRESA: PRODAM PROCESSAMENTO DE DADOS </t>
+          <t>-REFERENTE A PARTE DO SEGUNDO TERMO ADITIVO AO TERMO DE CONTRATO DE Nº 003/2015, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS - IDAM E A EMPR</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2017NE01609</t>
+          <t>2017NE01621</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>17/2014</t>
+          <t>4/2015</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -6906,7 +6906,7 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>1139.72</v>
+        <v>4517.98</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
@@ -6915,19 +6915,19 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t xml:space="preserve">-REFERENTE A PARTE DO TERCEIRO TERMO ADITIVO AO TERMO DE CONTRATO Nº 017/2014 FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS-IDAM E A EMPRESA: </t>
+          <t>Contratação de serviço de execução de sistemas PRODAM - RH, para manter o cadastro dos servidores e Folha de Pagamento de Pessoal, processar folhas de pagamento e fornecer relatórios para efetivação d</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2017NE01621</t>
+          <t>2017NE01609</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>4/2015</t>
+          <t>17/2014</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -6936,7 +6936,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>4517.98</v>
+        <v>1139.72</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -6945,19 +6945,19 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Contratação de serviço de execução de sistemas PRODAM - RH, para manter o cadastro dos servidores e Folha de Pagamento de Pessoal, processar folhas de pagamento e fornecer relatórios para efetivação d</t>
+          <t xml:space="preserve">-REFERENTE A PARTE DO TERCEIRO TERMO ADITIVO AO TERMO DE CONTRATO Nº 017/2014 FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS-IDAM E A EMPRESA: </t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2017NE01623</t>
+          <t>2017NE01615</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>3/2015</t>
+          <t>13/2017</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -6966,7 +6966,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>1934.28</v>
+        <v>12600</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>-REFERENTE A PARTE DO SEGUNDO TERMO ADITIVO AO TERMO DE CONTRATO DE Nº 003/2015, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS - IDAM E A EMPR</t>
+          <t xml:space="preserve">-REFERENTE A UM TERMO DE CONTRATO Nº 013/2017 FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS - IDAM E A EMPRESA: PRODAM PROCESSAMENTO DE DADOS </t>
         </is>
       </c>
     </row>
@@ -7012,12 +7012,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2016NE01012</t>
+          <t>2016NE01011</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>14/2013</t>
+          <t>8/2012</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -7026,7 +7026,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>12372.6</v>
+        <v>21045.39</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
@@ -7035,19 +7035,19 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t xml:space="preserve">-REFERENTE A PARTE DO SEGUNDO TERMO ADITIVO AO TERMO DE CONTRATO Nº 014/2013, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS-IDAM E A EMPRESA: </t>
+          <t>-REFERENTE PARTE DO QUARTO TERMO ADITIVO AO TERMO DE CONTRATO Nº 008/2012 FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS - IDAM E A EMPRESA: PR</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2016NE01011</t>
+          <t>2016NE01012</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>8/2012</t>
+          <t>14/2013</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -7056,7 +7056,7 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>21045.39</v>
+        <v>12372.6</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>-REFERENTE PARTE DO QUARTO TERMO ADITIVO AO TERMO DE CONTRATO Nº 008/2012 FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS - IDAM E A EMPRESA: PR</t>
+          <t xml:space="preserve">-REFERENTE A PARTE DO SEGUNDO TERMO ADITIVO AO TERMO DE CONTRATO Nº 014/2013, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS-IDAM E A EMPRESA: </t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2015NE00616</t>
+          <t>2015NE00612</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>14/2013</t>
+          <t>3/2015</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -7116,7 +7116,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>30972.55</v>
+        <v>14760.63</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
@@ -7125,19 +7125,19 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Cobertura Financeira 2015</t>
+          <t xml:space="preserve">COMPLEMENTAÇÃO QUE SE FAZ DO EMPENHO Nº 8/2015, REFERENTE A PARTE DE UM TERMO DE CONTRATO A SER FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS </t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2015NE00615</t>
+          <t>2015NE00614</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>8/2012</t>
+          <t>17/2014</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -7146,7 +7146,7 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>44367.47</v>
+        <v>6000</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
@@ -7192,12 +7192,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2015NE00614</t>
+          <t>2015NE00615</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>17/2014</t>
+          <t>8/2012</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -7206,7 +7206,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>6000</v>
+        <v>44367.47</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -7222,12 +7222,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2015NE00612</t>
+          <t>2015NE00616</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>3/2015</t>
+          <t>14/2013</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -7236,7 +7236,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>14760.63</v>
+        <v>30972.55</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMPLEMENTAÇÃO QUE SE FAZ DO EMPENHO Nº 8/2015, REFERENTE A PARTE DE UM TERMO DE CONTRATO A SER FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS </t>
+          <t>Cobertura Financeira 2015</t>
         </is>
       </c>
     </row>
@@ -7338,12 +7338,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2017NE00956</t>
+          <t>2017NE00957</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>3/2015</t>
+          <t>4/2015</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -7352,7 +7352,7 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>5802.84</v>
+        <v>13553.94</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
@@ -7361,19 +7361,19 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Contratação de empresa p/ serviços de Sist., p/ processamento do Sistema de Protoc. em plataforma Web (SPROWeb) obj. o controle e acomp. do regist. de todos os doc. ou processos dos clientes.</t>
+          <t>-REFERENTE A PARTE DO SEGUNDO TERMO ADITIVO AO TERMO DE CONTRATO Nº 004/2015, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS - IDAM E A EMPRESA</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2017NE00957</t>
+          <t>2017NE00956</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>4/2015</t>
+          <t>3/2015</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -7382,7 +7382,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>13553.94</v>
+        <v>5802.84</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>-REFERENTE A PARTE DO SEGUNDO TERMO ADITIVO AO TERMO DE CONTRATO Nº 004/2015, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS - IDAM E A EMPRESA</t>
+          <t>Contratação de empresa p/ serviços de Sist., p/ processamento do Sistema de Protoc. em plataforma Web (SPROWeb) obj. o controle e acomp. do regist. de todos os doc. ou processos dos clientes.</t>
         </is>
       </c>
     </row>
@@ -7428,7 +7428,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2018NE01453</t>
+          <t>2018NE01450</t>
         </is>
       </c>
       <c r="B242" t="inlineStr"/>
@@ -7438,7 +7438,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>128.4</v>
+        <v>0.4</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
@@ -7447,14 +7447,14 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>-ANULAÇÃO TOTAL QUE SE FAZ DA NE Nº 0780/2018 EMITIDA EM: 04/06/2018. EM VIRTUDE DA VIGÊNCIA DO CONTRATO.</t>
+          <t>-ANULAÇÃO TOTAL QUE SE FAZ DA NE Nº 0340/2018 EMITIDA EM: 01/03/2018. EM VIRTUDE DA VIGÊNCIA DO CONTRATO.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2018NE01449</t>
+          <t>2018NE01451</t>
         </is>
       </c>
       <c r="B243" t="inlineStr"/>
@@ -7464,7 +7464,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>10257.48</v>
+        <v>9132.24</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
@@ -7473,14 +7473,14 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>-ANULAÇÃO TOTAL QUE SE FAZ DA NE Nº 0336/2018 EMITIDA EM: 01/03/2018. EM VIRTUDE DA VIGÊNCIA DO CONTRATO.</t>
+          <t>-ANULAÇÃO TOTAL QUE SE FAZ DA NE Nº 0430/2018 EMITIDA EM: 23/03/2018. EM VIRTUDE DA VIGÊNCIA DO CONTRATO.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2018NE01451</t>
+          <t>2018NE01449</t>
         </is>
       </c>
       <c r="B244" t="inlineStr"/>
@@ -7490,7 +7490,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>9132.24</v>
+        <v>10257.48</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
@@ -7499,14 +7499,14 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>-ANULAÇÃO TOTAL QUE SE FAZ DA NE Nº 0430/2018 EMITIDA EM: 23/03/2018. EM VIRTUDE DA VIGÊNCIA DO CONTRATO.</t>
+          <t>-ANULAÇÃO TOTAL QUE SE FAZ DA NE Nº 0336/2018 EMITIDA EM: 01/03/2018. EM VIRTUDE DA VIGÊNCIA DO CONTRATO.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2018NE01450</t>
+          <t>2018NE01453</t>
         </is>
       </c>
       <c r="B245" t="inlineStr"/>
@@ -7516,7 +7516,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>0.4</v>
+        <v>128.4</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>-ANULAÇÃO TOTAL QUE SE FAZ DA NE Nº 0340/2018 EMITIDA EM: 01/03/2018. EM VIRTUDE DA VIGÊNCIA DO CONTRATO.</t>
+          <t>-ANULAÇÃO TOTAL QUE SE FAZ DA NE Nº 0780/2018 EMITIDA EM: 04/06/2018. EM VIRTUDE DA VIGÊNCIA DO CONTRATO.</t>
         </is>
       </c>
     </row>
@@ -7562,12 +7562,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2016NE01591</t>
+          <t>2016NE01590</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>14/2013</t>
+          <t>3/2015</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -7576,7 +7576,7 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>6120</v>
+        <v>1805.55</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
@@ -7585,19 +7585,19 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>-REFERENTE A PARTE DO TERCEIRO TERMO ADITIVO AO TERMO DE CONTRATO Nº 014/2013, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS-IDAM E A EMPRESA:</t>
+          <t>-REFERENTE A PARTE DO PRIMEIRO TERMO ADITIVO AO TERMO DE CONTRATO DE Nº 003/2015, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS - IDAM E A EMP</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2016NE01590</t>
+          <t>2016NE01591</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>3/2015</t>
+          <t>14/2013</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -7606,7 +7606,7 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>1805.55</v>
+        <v>6120</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>-REFERENTE A PARTE DO PRIMEIRO TERMO ADITIVO AO TERMO DE CONTRATO DE Nº 003/2015, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS - IDAM E A EMP</t>
+          <t>-REFERENTE A PARTE DO TERCEIRO TERMO ADITIVO AO TERMO DE CONTRATO Nº 014/2013, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS-IDAM E A EMPRESA:</t>
         </is>
       </c>
     </row>
@@ -7652,12 +7652,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2021NE0000078</t>
+          <t>2021NE0000077</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>7/2020</t>
+          <t>8/2020</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -7666,7 +7666,7 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>12341.86</v>
+        <v>5337.38</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
@@ -7675,19 +7675,19 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em manter o cadastro dos servidores e folha de pagamento pessoal, processar folhas de pagamento e fornecer relatórios para efetivação de pagamento.</t>
+          <t>Serviço de execução de sistema de protocolo em plataforma web, objetivando o controle e acompanhamento o controle e acompanhamento do registro de todos os documentos ou processos do cliente para atend</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2021NE0000077</t>
+          <t>2021NE0000078</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>8/2020</t>
+          <t>7/2020</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -7696,7 +7696,7 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>5337.38</v>
+        <v>12341.86</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Serviço de execução de sistema de protocolo em plataforma web, objetivando o controle e acompanhamento o controle e acompanhamento do registro de todos os documentos ou processos do cliente para atend</t>
+          <t>Contratação de empresa especializada em manter o cadastro dos servidores e folha de pagamento pessoal, processar folhas de pagamento e fornecer relatórios para efetivação de pagamento.</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2016NE01588</t>
+          <t>2016NE01587</t>
         </is>
       </c>
       <c r="B253" t="inlineStr"/>
@@ -7752,7 +7752,7 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>473.84</v>
+        <v>768.37</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
@@ -7768,7 +7768,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2016NE01587</t>
+          <t>2016NE01588</t>
         </is>
       </c>
       <c r="B254" t="inlineStr"/>
@@ -7778,7 +7778,7 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>768.37</v>
+        <v>473.84</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
@@ -7854,12 +7854,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2025NE0001154</t>
+          <t>2025NE0001156</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>5/2025</t>
+          <t>1/2024</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -7868,7 +7868,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>4123.26</v>
+        <v>8498.67</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de execução de sistema de protocolo web visando atender às necessidades do IDAM central.</t>
+          <t>Contratação de empresa especializada na prestação dos serviços de fornecimento de licença de uso de sistema de informação, disponibilizando o Gestor de Conteúdo Web para publicação de informações, not</t>
         </is>
       </c>
     </row>
@@ -7914,12 +7914,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>2025NE0001156</t>
+          <t>2025NE0001154</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>1/2024</t>
+          <t>5/2025</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>8498.67</v>
+        <v>4123.26</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
@@ -7937,19 +7937,19 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação dos serviços de fornecimento de licença de uso de sistema de informação, disponibilizando o Gestor de Conteúdo Web para publicação de informações, not</t>
+          <t>Contratação de empresa especializada na prestação de serviços de execução de sistema de protocolo web visando atender às necessidades do IDAM central.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2019NE00614</t>
+          <t>2019NE00618</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>13/2017</t>
+          <t>4/2015</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -7958,7 +7958,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>50813.46</v>
+        <v>14867.31</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
@@ -7967,19 +7967,19 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE ACESSO A INTERNET ESTABELECENDO CIRCUITO DE DADOS, DESTINADO A ATENDER AS NECESSIDADES DESTE ÓRGÃO. -VIGENCIA: 01/06/2019 A 31/05/2020 -VALOR GLOBAL </t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE EXECUÇÃO DE SISTEMAS PRODAM-RH, PARA MANTER O CADASTRO DOS SERVIDORES E FOLHA DE PAGAMENTO DE PESSOAL, PROCESSAR FOLHAS DE PAGAMENTO E FORNECER RELA</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2019NE00620</t>
+          <t>2019NE00622</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>3/2015</t>
+          <t>16/2018</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -7988,7 +7988,7 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>6429.54</v>
+        <v>4744.08</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
@@ -7997,19 +7997,19 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE EXECUÇÃO DE SISTEMA, PARA PROCESSAMENTO DO SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPROWeb)</t>
+          <t xml:space="preserve">CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB PARA PUBLICAÇÃO DE INFORMAÇÕES, NOTICIAS, VÍDEOS </t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2019NE00622</t>
+          <t>2019NE00620</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>16/2018</t>
+          <t>3/2015</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -8018,7 +8018,7 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>4744.08</v>
+        <v>6429.54</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
@@ -8027,19 +8027,19 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB PARA PUBLICAÇÃO DE INFORMAÇÕES, NOTICIAS, VÍDEOS </t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE EXECUÇÃO DE SISTEMA, PARA PROCESSAMENTO DO SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPROWeb)</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2019NE00618</t>
+          <t>2019NE00614</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>4/2015</t>
+          <t>13/2017</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -8048,7 +8048,7 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>14867.31</v>
+        <v>50813.46</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE EXECUÇÃO DE SISTEMAS PRODAM-RH, PARA MANTER O CADASTRO DOS SERVIDORES E FOLHA DE PAGAMENTO DE PESSOAL, PROCESSAR FOLHAS DE PAGAMENTO E FORNECER RELA</t>
+          <t xml:space="preserve">CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE ACESSO A INTERNET ESTABELECENDO CIRCUITO DE DADOS, DESTINADO A ATENDER AS NECESSIDADES DESTE ÓRGÃO. -VIGENCIA: 01/06/2019 A 31/05/2020 -VALOR GLOBAL </t>
         </is>
       </c>
     </row>
@@ -8090,12 +8090,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2025NE0000445</t>
+          <t>2025NE0000442</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>1/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -8104,7 +8104,7 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>2832.89</v>
+        <v>24097.98</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
@@ -8113,19 +8113,19 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação dos serviços de fornecimento de licença de uso de sistema de informação, disponibilizando o Gestor de Conteúdo Web para publicação de informações, not</t>
+          <t xml:space="preserve">Contratação de empresa especializada em serviço de acesso à rede de internet, para atender as necessidades do Instituto de Desenvolvimento Agropecuário e Florestal Sustentável do Estado do Amazonas – </t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2025NE0000444</t>
+          <t>2025NE0000443</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>6/2025</t>
+          <t>5/2025</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -8134,7 +8134,7 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>8574.6</v>
+        <v>1374.42</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
@@ -8143,19 +8143,19 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de execução e manutenção de sistema de Recursos Humanos (RH), para atender as necessidades do IDAM, pelo período de 12 (doze) meses</t>
+          <t>Contratação de empresa especializada na prestação de serviços de execução de sistema de protocolo web visando atender às necessidades do IDAM central.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2025NE0000443</t>
+          <t>2025NE0000444</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>5/2025</t>
+          <t>6/2025</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -8164,7 +8164,7 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>1374.42</v>
+        <v>8574.6</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
@@ -8173,19 +8173,19 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de execução de sistema de protocolo web visando atender às necessidades do IDAM central.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de execução e manutenção de sistema de Recursos Humanos (RH), para atender as necessidades do IDAM, pelo período de 12 (doze) meses</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2025NE0000442</t>
+          <t>2025NE0000445</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>1/2024</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>24097.98</v>
+        <v>2832.89</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
@@ -8203,19 +8203,19 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de empresa especializada em serviço de acesso à rede de internet, para atender as necessidades do Instituto de Desenvolvimento Agropecuário e Florestal Sustentável do Estado do Amazonas – </t>
+          <t>Contratação de empresa especializada na prestação dos serviços de fornecimento de licença de uso de sistema de informação, disponibilizando o Gestor de Conteúdo Web para publicação de informações, not</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2024NE0000424</t>
+          <t>2024NE0000443</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>1/2024</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -8224,7 +8224,7 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>46688.24</v>
+        <v>5435.32</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
@@ -8233,19 +8233,19 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de empresa especializada em serviço de acesso à rede de internet, para atender as necessidades do Instituto de Desenvolvimento Agropecuário e Florestal Sustentável do Estado do Amazonas – </t>
+          <t>Contratação de empresa especializada na prestação dos serviços de fornecimento de licença de uso de sistema de informação, disponibilizando o Gestor de Conteúdo Web para publicação de informações, not</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2024NE0000445</t>
+          <t>2024NE0000444</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>7/2020</t>
+          <t>8/2020</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -8254,7 +8254,7 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>12635.82</v>
+        <v>2473.48</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
@@ -8263,19 +8263,19 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em manter o cadastro dos servidores e folha de pagamento pessoal, processar folhas de pagamento e fornecer relatórios para efetivação de pagamento. TC: 0007/2020 A</t>
+          <t>Contratação de Serviço de execução de sistema de protocolo em plataforma web, objetivando o controle e acompanhamento o controle e acompanhamento do registro de todos os documentos ou processos do cli</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2024NE0000444</t>
+          <t>2024NE0000445</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>8/2020</t>
+          <t>7/2020</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -8284,7 +8284,7 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>2473.48</v>
+        <v>12635.82</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
@@ -8293,19 +8293,19 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Contratação de Serviço de execução de sistema de protocolo em plataforma web, objetivando o controle e acompanhamento o controle e acompanhamento do registro de todos os documentos ou processos do cli</t>
+          <t>Contratação de empresa especializada em manter o cadastro dos servidores e folha de pagamento pessoal, processar folhas de pagamento e fornecer relatórios para efetivação de pagamento. TC: 0007/2020 A</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2024NE0000443</t>
+          <t>2024NE0000424</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>1/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -8314,7 +8314,7 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>5435.32</v>
+        <v>46688.24</v>
       </c>
       <c r="E272" t="inlineStr">
         <is>
@@ -8323,7 +8323,7 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação dos serviços de fornecimento de licença de uso de sistema de informação, disponibilizando o Gestor de Conteúdo Web para publicação de informações, not</t>
+          <t xml:space="preserve">Contratação de empresa especializada em serviço de acesso à rede de internet, para atender as necessidades do Instituto de Desenvolvimento Agropecuário e Florestal Sustentável do Estado do Amazonas – </t>
         </is>
       </c>
     </row>
@@ -8390,12 +8390,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>2016NE01343</t>
+          <t>2016NE01345</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>3/2015</t>
+          <t>14/2013</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -8404,7 +8404,7 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>1805.55</v>
+        <v>6120</v>
       </c>
       <c r="E275" t="inlineStr">
         <is>
@@ -8413,19 +8413,19 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>-REFERENTE A PARTE DO PRIMEIRO TERMO ADITIVO AO TERMO DE CONTRATO DE Nº 003/2015, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS - IDAM E A EMP</t>
+          <t>-REFERENTE A PARTE DO TERCEIRO TERMO ADITIVO AO TERMO DE CONTRATO Nº 014/2013, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS-IDAM E A EMPRESA:</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>2016NE01343</t>
+          <t>2016NE01344</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>3/2015</t>
+          <t>8/2012</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -8434,7 +8434,7 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>1805.55</v>
+        <v>7015.13</v>
       </c>
       <c r="E276" t="inlineStr">
         <is>
@@ -8443,19 +8443,19 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>-REFERENTE A PARTE DO PRIMEIRO TERMO ADITIVO AO TERMO DE CONTRATO DE Nº 003/2015, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS - IDAM E A EMP</t>
+          <t>-REFERENTE PARTE DO QUARTO TERMO ADITIVO AO TERMO DE CONTRATO Nº 008/2012 FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS - IDAM E A EMPRESA: PR</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2016NE01345</t>
+          <t>2016NE01344</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>14/2013</t>
+          <t>8/2012</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -8464,7 +8464,7 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>6120</v>
+        <v>7015.13</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
@@ -8473,19 +8473,19 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>-REFERENTE A PARTE DO TERCEIRO TERMO ADITIVO AO TERMO DE CONTRATO Nº 014/2013, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS-IDAM E A EMPRESA:</t>
+          <t>-REFERENTE PARTE DO QUARTO TERMO ADITIVO AO TERMO DE CONTRATO Nº 008/2012 FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS - IDAM E A EMPRESA: PR</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>2016NE01344</t>
+          <t>2016NE01345</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>8/2012</t>
+          <t>14/2013</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -8494,7 +8494,7 @@
         </is>
       </c>
       <c r="D278" t="n">
-        <v>7015.13</v>
+        <v>6120</v>
       </c>
       <c r="E278" t="inlineStr">
         <is>
@@ -8503,19 +8503,19 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>-REFERENTE PARTE DO QUARTO TERMO ADITIVO AO TERMO DE CONTRATO Nº 008/2012 FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS - IDAM E A EMPRESA: PR</t>
+          <t>-REFERENTE A PARTE DO TERCEIRO TERMO ADITIVO AO TERMO DE CONTRATO Nº 014/2013, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS-IDAM E A EMPRESA:</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>2016NE01344</t>
+          <t>2016NE01343</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>8/2012</t>
+          <t>3/2015</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -8524,7 +8524,7 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>7015.13</v>
+        <v>1805.55</v>
       </c>
       <c r="E279" t="inlineStr">
         <is>
@@ -8533,19 +8533,19 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>-REFERENTE PARTE DO QUARTO TERMO ADITIVO AO TERMO DE CONTRATO Nº 008/2012 FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS - IDAM E A EMPRESA: PR</t>
+          <t>-REFERENTE A PARTE DO PRIMEIRO TERMO ADITIVO AO TERMO DE CONTRATO DE Nº 003/2015, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS - IDAM E A EMP</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2016NE01345</t>
+          <t>2016NE01343</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>14/2013</t>
+          <t>3/2015</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -8554,7 +8554,7 @@
         </is>
       </c>
       <c r="D280" t="n">
-        <v>6120</v>
+        <v>1805.55</v>
       </c>
       <c r="E280" t="inlineStr">
         <is>
@@ -8563,19 +8563,19 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>-REFERENTE A PARTE DO TERCEIRO TERMO ADITIVO AO TERMO DE CONTRATO Nº 014/2013, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS-IDAM E A EMPRESA:</t>
+          <t>-REFERENTE A PARTE DO PRIMEIRO TERMO ADITIVO AO TERMO DE CONTRATO DE Nº 003/2015, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS - IDAM E A EMP</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2025NE0000168</t>
+          <t>2025NE0000161</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>6/2025</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -8584,7 +8584,7 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>17149.2</v>
+        <v>48195.96</v>
       </c>
       <c r="E281" t="inlineStr">
         <is>
@@ -8593,7 +8593,7 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de execução e manutenção de sistema de Recursos Humanos (RH), para atender as necessidades do IDAM, pelo período de 12 (doze) meses</t>
+          <t xml:space="preserve">Contratação de empresa especializada em serviço de acesso à rede de internet, para atender as necessidades do Instituto de Desenvolvimento Agropecuário e Florestal Sustentável do Estado do Amazonas – </t>
         </is>
       </c>
     </row>
@@ -8630,12 +8630,12 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2025NE0000161</t>
+          <t>2025NE0000168</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>6/2025</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -8644,7 +8644,7 @@
         </is>
       </c>
       <c r="D283" t="n">
-        <v>48195.96</v>
+        <v>17149.2</v>
       </c>
       <c r="E283" t="inlineStr">
         <is>
@@ -8653,14 +8653,14 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de empresa especializada em serviço de acesso à rede de internet, para atender as necessidades do Instituto de Desenvolvimento Agropecuário e Florestal Sustentável do Estado do Amazonas – </t>
+          <t>Contratação de empresa especializada na prestação de serviços de execução e manutenção de sistema de Recursos Humanos (RH), para atender as necessidades do IDAM, pelo período de 12 (doze) meses</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2022NE0001647</t>
+          <t>2022NE0001649</t>
         </is>
       </c>
       <c r="B284" t="inlineStr"/>
@@ -8670,7 +8670,7 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>2636.68</v>
+        <v>38.93</v>
       </c>
       <c r="E284" t="inlineStr">
         <is>
@@ -8686,7 +8686,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2022NE0001648</t>
+          <t>2022NE0001646</t>
         </is>
       </c>
       <c r="B285" t="inlineStr"/>
@@ -8696,7 +8696,7 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>4440.86</v>
+        <v>1155.72</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2022NE0001646</t>
+          <t>2022NE0001648</t>
         </is>
       </c>
       <c r="B286" t="inlineStr"/>
@@ -8722,7 +8722,7 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>1155.72</v>
+        <v>4440.86</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2022NE0001649</t>
+          <t>2022NE0001647</t>
         </is>
       </c>
       <c r="B287" t="inlineStr"/>
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>38.93</v>
+        <v>2636.68</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
@@ -8794,12 +8794,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2019NE00255</t>
+          <t>2019NE00253</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>3/2015</t>
+          <t>23/2015</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -8808,7 +8808,7 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>6429.54</v>
+        <v>79843.89999999999</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
@@ -8817,19 +8817,19 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Contratação de empresa p/ serviços de Sist., p/ processamento do Sistema de Protoc. em plataforma Web (SPROWEB) obj. o controle e acomp. do regist. de todos os doc. ou processos dos clientes.</t>
+          <t>Contratação de serviços de sistemas de informação, compreendendo o desenvolvimento e implantação do sistema de Gestão e Fomento de Assist.Téc.,Ext.Rural e Florestal - ATER</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>2019NE00254</t>
+          <t>2019NE00256</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>16/2018</t>
+          <t>4/2015</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -8838,7 +8838,7 @@
         </is>
       </c>
       <c r="D290" t="n">
-        <v>4744.08</v>
+        <v>14867.31</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
@@ -8847,7 +8847,7 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB PARA PUBLICAÇÃO DE INFORMAÇÕES, NOTÍCIAS, VÍDEO E IMAGENS VIA WEBSITE.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE EXECUÇÃO DE SISTEMAS PRODAM-RH, PARA MANTER O CADASTRO DOS SERVIDORES E FOLHA DE PAGAMENTO DE PESSOAL, PROCESSAR FOLHAS DE PAGAMENTO E FORNECER RELA</t>
         </is>
       </c>
     </row>
@@ -8884,12 +8884,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2019NE00256</t>
+          <t>2019NE00254</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>4/2015</t>
+          <t>16/2018</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -8898,7 +8898,7 @@
         </is>
       </c>
       <c r="D292" t="n">
-        <v>14867.31</v>
+        <v>4744.08</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
@@ -8907,19 +8907,19 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE EXECUÇÃO DE SISTEMAS PRODAM-RH, PARA MANTER O CADASTRO DOS SERVIDORES E FOLHA DE PAGAMENTO DE PESSOAL, PROCESSAR FOLHAS DE PAGAMENTO E FORNECER RELA</t>
+          <t>CONTRATAÇÃO DE SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB PARA PUBLICAÇÃO DE INFORMAÇÕES, NOTÍCIAS, VÍDEO E IMAGENS VIA WEBSITE.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2019NE00253</t>
+          <t>2019NE00255</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>23/2015</t>
+          <t>3/2015</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -8928,7 +8928,7 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>79843.89999999999</v>
+        <v>6429.54</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
@@ -8937,7 +8937,7 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Contratação de serviços de sistemas de informação, compreendendo o desenvolvimento e implantação do sistema de Gestão e Fomento de Assist.Téc.,Ext.Rural e Florestal - ATER</t>
+          <t>Contratação de empresa p/ serviços de Sist., p/ processamento do Sistema de Protoc. em plataforma Web (SPROWEB) obj. o controle e acomp. do regist. de todos os doc. ou processos dos clientes.</t>
         </is>
       </c>
     </row>
@@ -8974,12 +8974,12 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2026NE0000007</t>
+          <t>2026NE0000008</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>6/2025</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -8988,7 +8988,7 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>101519.88</v>
+        <v>17149.2</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de empresa especializada em serviço de acesso à rede de internet, para atender as necessidades do Instituto de Desenvolvimento Agropecuário e Florestal Sustentável do Estado do Amazonas – </t>
+          <t>Contratação de empresa especializada na prestação de serviços de execução e manutenção de sistema de Recursos Humanos (RH), para atender as necessidades do IDAM, pelo período de 12 (doze) meses</t>
         </is>
       </c>
     </row>
@@ -9034,12 +9034,12 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2026NE0000008</t>
+          <t>2026NE0000007</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>6/2025</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>17149.2</v>
+        <v>101519.88</v>
       </c>
       <c r="E297" t="inlineStr">
         <is>
@@ -9057,19 +9057,19 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de execução e manutenção de sistema de Recursos Humanos (RH), para atender as necessidades do IDAM, pelo período de 12 (doze) meses</t>
+          <t xml:space="preserve">Contratação de empresa especializada em serviço de acesso à rede de internet, para atender as necessidades do Instituto de Desenvolvimento Agropecuário e Florestal Sustentável do Estado do Amazonas – </t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2015NE00005</t>
+          <t>2015NE00068</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>3/2010</t>
+          <t>3/2015</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -9078,7 +9078,7 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>1584</v>
+        <v>3280.14</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
@@ -9087,19 +9087,19 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>-REFERENTE A PARTE DO QUARTO TERMO ADITIVO AO TERMO DE CONTRATO Nº 003/2010, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS - IDAM E A EMPRESA:</t>
+          <t>-REFERENTE A PARTE DE UM TERMO DE CONTRATO A SER FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS - IDAM E A EMPRESA: PRODAM PROCESSAMENTO DE DAD</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>2015NE00069</t>
+          <t>2015NE00029</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>8/2012</t>
+          <t>14/2013</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -9108,7 +9108,7 @@
         </is>
       </c>
       <c r="D299" t="n">
-        <v>12314.36</v>
+        <v>18583.53</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
@@ -9117,19 +9117,19 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Cobertura Financeira 2015 - meses: janeiro e fevereiro</t>
+          <t>-ANULAÇÃO TOTAL QUE SE FAZ DA NOTA DE EMPENHO Nº 26 EMITIDA EM 05/01/2015, POR MOTIVO DE EQUIVOCO NA NATUREZA DE DESPESA.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2015NE00067</t>
+          <t>2015NE00030</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>4/2015</t>
+          <t>14/2013</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -9138,7 +9138,7 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>16360.23</v>
+        <v>18583.53</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
@@ -9147,19 +9147,19 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>-REFERENTE A PARTE DE UM TERMO DE CONTRATO A SER FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS - IDAM E A EMPRESA: PRODAM PROCESSAMENTO DE DAD</t>
+          <t>Cobertura Financeira 2015 - meses: janeiro a março.</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2015NE00026</t>
+          <t>2015NE00027</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>14/2013</t>
+          <t>17/2014</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -9168,7 +9168,7 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>18583.53</v>
+        <v>3000</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
@@ -9177,19 +9177,19 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>-REFERENTE SALDO DO PRIMEIRO TERMO ADITIVO AO TERMO DE CONTRATO Nº 014/2013, A SER FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS-IDAM E A EMPR</t>
+          <t>Cobertura Financeira 2015 - meses: janeiro a março.</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2015NE00027</t>
+          <t>2015NE00026</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>17/2014</t>
+          <t>14/2013</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -9198,7 +9198,7 @@
         </is>
       </c>
       <c r="D302" t="n">
-        <v>3000</v>
+        <v>18583.53</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
@@ -9207,19 +9207,19 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Cobertura Financeira 2015 - meses: janeiro a março.</t>
+          <t>-REFERENTE SALDO DO PRIMEIRO TERMO ADITIVO AO TERMO DE CONTRATO Nº 014/2013, A SER FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS-IDAM E A EMPR</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2015NE00030</t>
+          <t>2015NE00067</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>14/2013</t>
+          <t>4/2015</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>18583.53</v>
+        <v>16360.23</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
@@ -9237,19 +9237,19 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Cobertura Financeira 2015 - meses: janeiro a março.</t>
+          <t>-REFERENTE A PARTE DE UM TERMO DE CONTRATO A SER FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS - IDAM E A EMPRESA: PRODAM PROCESSAMENTO DE DAD</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>2015NE00029</t>
+          <t>2015NE00069</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>14/2013</t>
+          <t>8/2012</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -9258,7 +9258,7 @@
         </is>
       </c>
       <c r="D304" t="n">
-        <v>18583.53</v>
+        <v>12314.36</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
@@ -9267,19 +9267,19 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>-ANULAÇÃO TOTAL QUE SE FAZ DA NOTA DE EMPENHO Nº 26 EMITIDA EM 05/01/2015, POR MOTIVO DE EQUIVOCO NA NATUREZA DE DESPESA.</t>
+          <t>Cobertura Financeira 2015 - meses: janeiro e fevereiro</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2015NE00068</t>
+          <t>2015NE00005</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>3/2015</t>
+          <t>3/2010</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -9288,7 +9288,7 @@
         </is>
       </c>
       <c r="D305" t="n">
-        <v>3280.14</v>
+        <v>1584</v>
       </c>
       <c r="E305" t="inlineStr">
         <is>
@@ -9297,14 +9297,14 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>-REFERENTE A PARTE DE UM TERMO DE CONTRATO A SER FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS - IDAM E A EMPRESA: PRODAM PROCESSAMENTO DE DAD</t>
+          <t>-REFERENTE A PARTE DO QUARTO TERMO ADITIVO AO TERMO DE CONTRATO Nº 003/2010, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS - IDAM E A EMPRESA:</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>2019NE01422</t>
+          <t>2019NE01421</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -9318,7 +9318,7 @@
         </is>
       </c>
       <c r="D306" t="n">
-        <v>15182.52</v>
+        <v>2582.52</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
@@ -9327,28 +9327,24 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>2º TERMO ADITIVO AO TERMO DE CONTRATO Nº 013/2017. -OBJETO: CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE ACESSO A INTERNET ESTABELECENDO CIRCUITO DE DADOS, DESTINADO A ATENDER AS NECESSIDADES DE</t>
+          <t>2º TERMO ADITIVO AO TERMO DE CONTRATO Nº 013/2017. -OBJETO: EMPRESA ESPECIALIZADA EM SERVIÇO DE ACESSO A INTERNET ESTABELECENDO CIRCUITO DE DADOS, DESTINADO A ATENDER AS NECESSIDADES DESTE ÓRGÃO. NF N</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>2019NE01442</t>
-        </is>
-      </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>13/2017</t>
-        </is>
-      </c>
+          <t>2019NE01424</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr"/>
       <c r="C307" t="inlineStr">
         <is>
           <t>04/12/2019</t>
         </is>
       </c>
       <c r="D307" t="n">
-        <v>12600</v>
+        <v>15182.52</v>
       </c>
       <c r="E307" t="inlineStr">
         <is>
@@ -9357,24 +9353,28 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE ACESSO A INTERNET ESTABELECENDO CIRCUITO DE DADOS, DESTINADO A ATENDER AS NECESSIDADES DESTE ÓRGÃO. -VIGENCIA: 02/06/2018 A 01/06/2019 NF Nº 5490 EMI</t>
+          <t>-ANULAÇÃO TOTAL QUE SE FAZ DA NE Nº 1422/2019, EM VIRTUDE DO EQUIVOCO NO VALOR.</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2019NE01424</t>
-        </is>
-      </c>
-      <c r="B308" t="inlineStr"/>
+          <t>2019NE01442</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>13/2017</t>
+        </is>
+      </c>
       <c r="C308" t="inlineStr">
         <is>
           <t>04/12/2019</t>
         </is>
       </c>
       <c r="D308" t="n">
-        <v>15182.52</v>
+        <v>12600</v>
       </c>
       <c r="E308" t="inlineStr">
         <is>
@@ -9383,14 +9383,14 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>-ANULAÇÃO TOTAL QUE SE FAZ DA NE Nº 1422/2019, EM VIRTUDE DO EQUIVOCO NO VALOR.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE ACESSO A INTERNET ESTABELECENDO CIRCUITO DE DADOS, DESTINADO A ATENDER AS NECESSIDADES DESTE ÓRGÃO. -VIGENCIA: 02/06/2018 A 01/06/2019 NF Nº 5490 EMI</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>2019NE01421</t>
+          <t>2019NE01422</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -9404,7 +9404,7 @@
         </is>
       </c>
       <c r="D309" t="n">
-        <v>2582.52</v>
+        <v>15182.52</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>2º TERMO ADITIVO AO TERMO DE CONTRATO Nº 013/2017. -OBJETO: EMPRESA ESPECIALIZADA EM SERVIÇO DE ACESSO A INTERNET ESTABELECENDO CIRCUITO DE DADOS, DESTINADO A ATENDER AS NECESSIDADES DESTE ÓRGÃO. NF N</t>
+          <t>2º TERMO ADITIVO AO TERMO DE CONTRATO Nº 013/2017. -OBJETO: CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE ACESSO A INTERNET ESTABELECENDO CIRCUITO DE DADOS, DESTINADO A ATENDER AS NECESSIDADES DE</t>
         </is>
       </c>
     </row>
@@ -9480,12 +9480,12 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>2023NE0001234</t>
+          <t>2023NE01229</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>16/2018</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -9494,7 +9494,7 @@
         </is>
       </c>
       <c r="D312" t="n">
-        <v>5341.96</v>
+        <v>46688.24</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
@@ -9503,19 +9503,19 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB PARA PUBLICAÇÃO DE INFORMAÇÕES, NOTÍCIAS, VÍDEO E IMAGENS VIA WEBSITE. TC</t>
+          <t>Contratação de empresa especializada em serviço de acesso à rede de internet.</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>2023NE0001233</t>
+          <t>2023NE0001232</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>7/2020</t>
+          <t>8/2020</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -9524,7 +9524,7 @@
         </is>
       </c>
       <c r="D313" t="n">
-        <v>15910.12</v>
+        <v>2473.48</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
@@ -9533,7 +9533,7 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em manter o cadastro dos servidores e folha de pagamento pessoal, processar folhas de pagamento e fornecer relatórios para efetivação de pagamento. TC: 007/2020 AD</t>
+          <t>Contratação de Serviço de execução de sistema de protocolo em plataforma web, objetivando o controle e acompanhamento o controle e acompanhamento do registro de todos os documentos ou processos do cli</t>
         </is>
       </c>
     </row>
@@ -9570,12 +9570,12 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2023NE0001232</t>
+          <t>2023NE0001233</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>8/2020</t>
+          <t>7/2020</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -9584,7 +9584,7 @@
         </is>
       </c>
       <c r="D315" t="n">
-        <v>2473.48</v>
+        <v>15910.12</v>
       </c>
       <c r="E315" t="inlineStr">
         <is>
@@ -9593,19 +9593,19 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Contratação de Serviço de execução de sistema de protocolo em plataforma web, objetivando o controle e acompanhamento o controle e acompanhamento do registro de todos os documentos ou processos do cli</t>
+          <t>Contratação de empresa especializada em manter o cadastro dos servidores e folha de pagamento pessoal, processar folhas de pagamento e fornecer relatórios para efetivação de pagamento. TC: 007/2020 AD</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>2023NE01229</t>
+          <t>2023NE0001234</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>16/2018</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -9614,7 +9614,7 @@
         </is>
       </c>
       <c r="D316" t="n">
-        <v>46688.24</v>
+        <v>5341.96</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviço de acesso à rede de internet.</t>
+          <t>CONTRATAÇÃO DE SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB PARA PUBLICAÇÃO DE INFORMAÇÕES, NOTÍCIAS, VÍDEO E IMAGENS VIA WEBSITE. TC</t>
         </is>
       </c>
     </row>
@@ -9660,12 +9660,12 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>2023NE0000721</t>
+          <t>2023NE0000722</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>7/2020</t>
+          <t>16/2018</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -9674,7 +9674,7 @@
         </is>
       </c>
       <c r="D318" t="n">
-        <v>15910.12</v>
+        <v>5341.96</v>
       </c>
       <c r="E318" t="inlineStr">
         <is>
@@ -9683,7 +9683,7 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em manter o cadastro dos servidores e folha de pagamento pessoal, processar folhas de pagamento e fornecer relatórios para efetivação de pagamento. TC: 007/2020 AD</t>
+          <t>CONTRATAÇÃO DE SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB PARA PUBLICAÇÃO DE INFORMAÇÕES, NOTÍCIAS, VÍDEO E IMAGENS VIA WEBSITE. TC</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>2023NE0000722</t>
+          <t>2023NE0000721</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>16/2018</t>
+          <t>7/2020</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -9734,7 +9734,7 @@
         </is>
       </c>
       <c r="D320" t="n">
-        <v>5341.96</v>
+        <v>15910.12</v>
       </c>
       <c r="E320" t="inlineStr">
         <is>
@@ -9743,19 +9743,19 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB PARA PUBLICAÇÃO DE INFORMAÇÕES, NOTÍCIAS, VÍDEO E IMAGENS VIA WEBSITE. TC</t>
+          <t>Contratação de empresa especializada em manter o cadastro dos servidores e folha de pagamento pessoal, processar folhas de pagamento e fornecer relatórios para efetivação de pagamento. TC: 007/2020 AD</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>2021NE0000561</t>
+          <t>2021NE0000560</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>8/2020</t>
+          <t>7/2020</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -9764,7 +9764,7 @@
         </is>
       </c>
       <c r="D321" t="n">
-        <v>10674.76</v>
+        <v>24683.72</v>
       </c>
       <c r="E321" t="inlineStr">
         <is>
@@ -9773,19 +9773,19 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>-PRIMEIRO TERMO ADITIVO AO TERMO DE CONTRATO Nº 008/2020. -OBJETO: CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE EXECUÇÃO DE SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPROWeb), OBJETIVANDO O CONTR</t>
+          <t xml:space="preserve">-PRIMEIRO TERMO ADITIVO AO TERMO DE CONTRATO Nº 007/2020. -OBJETO: CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE EXECUÇÃO DE SISTEMAS PRODAM-RH, PARA MANTER O CADASTRO DOS SERVIDORES E FOLHA DE </t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>2021NE0000560</t>
+          <t>2021NE0000561</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>7/2020</t>
+          <t>8/2020</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -9794,7 +9794,7 @@
         </is>
       </c>
       <c r="D322" t="n">
-        <v>24683.72</v>
+        <v>10674.76</v>
       </c>
       <c r="E322" t="inlineStr">
         <is>
@@ -9803,7 +9803,7 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t xml:space="preserve">-PRIMEIRO TERMO ADITIVO AO TERMO DE CONTRATO Nº 007/2020. -OBJETO: CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE EXECUÇÃO DE SISTEMAS PRODAM-RH, PARA MANTER O CADASTRO DOS SERVIDORES E FOLHA DE </t>
+          <t>-PRIMEIRO TERMO ADITIVO AO TERMO DE CONTRATO Nº 008/2020. -OBJETO: CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE EXECUÇÃO DE SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPROWeb), OBJETIVANDO O CONTR</t>
         </is>
       </c>
     </row>
@@ -9840,12 +9840,12 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>2021NE0000072</t>
+          <t>2021NE0000071</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>8/2020</t>
+          <t>16/2018</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -9854,7 +9854,7 @@
         </is>
       </c>
       <c r="D324" t="n">
-        <v>1064.05</v>
+        <v>687.83</v>
       </c>
       <c r="E324" t="inlineStr">
         <is>
@@ -9863,19 +9863,19 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>NF nº 15279 emitida em 18/06/2020, no valor de R$ 1.064,05, referente ao mês de junho/2020 - PRODAM, contrato nº 08/2020, serviços de execução de sistema de protocolo em plataforma web (sproweb), obje</t>
+          <t>NF nº 18474 emitida em: 23/12/2020, no valor de R$ 687,83, referente ao mês de dezembro/2020 – PRODAM contrato nº 016/2018, serviço de licença de uso de sistema de informação, compreendendo a disponib</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>2021NE0000071</t>
+          <t>2021NE0000072</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>16/2018</t>
+          <t>8/2020</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -9884,7 +9884,7 @@
         </is>
       </c>
       <c r="D325" t="n">
-        <v>687.83</v>
+        <v>1064.05</v>
       </c>
       <c r="E325" t="inlineStr">
         <is>
@@ -9893,19 +9893,19 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>NF nº 18474 emitida em: 23/12/2020, no valor de R$ 687,83, referente ao mês de dezembro/2020 – PRODAM contrato nº 016/2018, serviço de licença de uso de sistema de informação, compreendendo a disponib</t>
+          <t>NF nº 15279 emitida em 18/06/2020, no valor de R$ 1.064,05, referente ao mês de junho/2020 - PRODAM, contrato nº 08/2020, serviços de execução de sistema de protocolo em plataforma web (sproweb), obje</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>2021NE0000014</t>
+          <t>2021NE0000011</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>16/2018</t>
+          <t>13/2017</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -9914,7 +9914,7 @@
         </is>
       </c>
       <c r="D326" t="n">
-        <v>20635.01</v>
+        <v>84689.10000000001</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
@@ -9923,19 +9923,19 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB PARA PUBLICAÇÃO DE INFORMAÇÕES, NOTÍCIAS, VÍDEO E IMAGENS VIA WEBSITE.</t>
+          <t>Contratação de empresa especializada em serviços de acesso a rede de internet, estabelecendo comunicação a partir de circuito de dados existentes entre a contratante e a contratada.</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>2021NE0000006</t>
+          <t>2021NE0000007</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>7/2020</t>
+          <t>8/2020</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -9944,7 +9944,7 @@
         </is>
       </c>
       <c r="D327" t="n">
-        <v>9911.540000000001</v>
+        <v>4286.36</v>
       </c>
       <c r="E327" t="inlineStr">
         <is>
@@ -9953,19 +9953,19 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>contratação de empresa especializada em manter o cadastro dos servidores e folha de pagamento pessoal, processar folhas de pagamento e fornecer relatórios para efetivação de pagamento.</t>
+          <t>Serviço de execução de sistema de protocolo em plataforma web, objetivando o controle e acompanhamento o controle e acompanhamento do registro de todos os documentos ou processos do cliente para atend</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>2021NE0000007</t>
+          <t>2021NE0000006</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>8/2020</t>
+          <t>7/2020</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -9974,7 +9974,7 @@
         </is>
       </c>
       <c r="D328" t="n">
-        <v>4286.36</v>
+        <v>9911.540000000001</v>
       </c>
       <c r="E328" t="inlineStr">
         <is>
@@ -9983,19 +9983,19 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Serviço de execução de sistema de protocolo em plataforma web, objetivando o controle e acompanhamento o controle e acompanhamento do registro de todos os documentos ou processos do cliente para atend</t>
+          <t>contratação de empresa especializada em manter o cadastro dos servidores e folha de pagamento pessoal, processar folhas de pagamento e fornecer relatórios para efetivação de pagamento.</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>2021NE0000011</t>
+          <t>2021NE0000014</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>13/2017</t>
+          <t>16/2018</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -10004,7 +10004,7 @@
         </is>
       </c>
       <c r="D329" t="n">
-        <v>84689.10000000001</v>
+        <v>20635.01</v>
       </c>
       <c r="E329" t="inlineStr">
         <is>
@@ -10013,19 +10013,19 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviços de acesso a rede de internet, estabelecendo comunicação a partir de circuito de dados existentes entre a contratante e a contratada.</t>
+          <t>CONTRATAÇÃO DE SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB PARA PUBLICAÇÃO DE INFORMAÇÕES, NOTÍCIAS, VÍDEO E IMAGENS VIA WEBSITE.</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>2016NE00066</t>
+          <t>2016NE00070</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>17/2014</t>
+          <t>23/2015</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -10034,7 +10034,7 @@
         </is>
       </c>
       <c r="D330" t="n">
-        <v>6000</v>
+        <v>119765.85</v>
       </c>
       <c r="E330" t="inlineStr">
         <is>
@@ -10043,19 +10043,19 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>-REFERENTE A PARTE DO PRIMEIRO TERMO ADITIVO AO DO TERMO DE CONTRATO Nº 017/2014 FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS-IDAM E A EMPRES</t>
+          <t>cobertura Financeira</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>2016NE00082</t>
+          <t>2016NE00083</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>3/2015</t>
+          <t>4/2015</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -10064,7 +10064,7 @@
         </is>
       </c>
       <c r="D331" t="n">
-        <v>1640.07</v>
+        <v>4517.98</v>
       </c>
       <c r="E331" t="inlineStr">
         <is>
@@ -10073,19 +10073,19 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>-REFERENTE A PARTE DO TERMO DE CONTRATO DE Nº 003/2015, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS - IDAM E A EMPRESA: PRODAM PROCESSAMENTO</t>
+          <t>-REFERENTE A PARTE DO TERMO DE CONTRATO Nº 004/2015, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS - IDAM E A EMPRESA: PRODAM PROCESSAMENTO DE</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>2016NE00070</t>
+          <t>2016NE00063</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>23/2015</t>
+          <t>14/2013</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -10094,7 +10094,7 @@
         </is>
       </c>
       <c r="D332" t="n">
-        <v>119765.85</v>
+        <v>37117.8</v>
       </c>
       <c r="E332" t="inlineStr">
         <is>
@@ -10103,7 +10103,7 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>-REFERENTE A PARTE DO TERMO DE CONTRATO DE Nº 023/2015, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS-IDAM E A EMPRESA: PRODAM PROCESSAMENTO D</t>
+          <t xml:space="preserve">-REFERENTE A PARTE DO SEGUNDO TERMO ADITIVO AO TERMO DE CONTRATO Nº 014/2013, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS-IDAM E A EMPRESA: </t>
         </is>
       </c>
     </row>
@@ -10140,12 +10140,12 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>2016NE00063</t>
+          <t>2016NE00070</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>14/2013</t>
+          <t>23/2015</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -10154,7 +10154,7 @@
         </is>
       </c>
       <c r="D334" t="n">
-        <v>37117.8</v>
+        <v>119765.85</v>
       </c>
       <c r="E334" t="inlineStr">
         <is>
@@ -10163,19 +10163,19 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t xml:space="preserve">-REFERENTE A PARTE DO SEGUNDO TERMO ADITIVO AO TERMO DE CONTRATO Nº 014/2013, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS-IDAM E A EMPRESA: </t>
+          <t>-REFERENTE A PARTE DO TERMO DE CONTRATO DE Nº 023/2015, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS-IDAM E A EMPRESA: PRODAM PROCESSAMENTO D</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>2016NE00083</t>
+          <t>2016NE00082</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>4/2015</t>
+          <t>3/2015</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -10184,7 +10184,7 @@
         </is>
       </c>
       <c r="D335" t="n">
-        <v>4517.98</v>
+        <v>1640.07</v>
       </c>
       <c r="E335" t="inlineStr">
         <is>
@@ -10193,19 +10193,19 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>-REFERENTE A PARTE DO TERMO DE CONTRATO Nº 004/2015, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS - IDAM E A EMPRESA: PRODAM PROCESSAMENTO DE</t>
+          <t>-REFERENTE A PARTE DO TERMO DE CONTRATO DE Nº 003/2015, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS - IDAM E A EMPRESA: PRODAM PROCESSAMENTO</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>2016NE00070</t>
+          <t>2016NE00066</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>23/2015</t>
+          <t>17/2014</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -10214,7 +10214,7 @@
         </is>
       </c>
       <c r="D336" t="n">
-        <v>119765.85</v>
+        <v>6000</v>
       </c>
       <c r="E336" t="inlineStr">
         <is>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>cobertura Financeira</t>
+          <t>-REFERENTE A PARTE DO PRIMEIRO TERMO ADITIVO AO DO TERMO DE CONTRATO Nº 017/2014 FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS-IDAM E A EMPRES</t>
         </is>
       </c>
     </row>
@@ -10256,12 +10256,12 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>2019NE01098</t>
+          <t>2019NE01097</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>16/2018</t>
+          <t>4/2015</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -10270,7 +10270,7 @@
         </is>
       </c>
       <c r="D338" t="n">
-        <v>3162.72</v>
+        <v>14867.31</v>
       </c>
       <c r="E338" t="inlineStr">
         <is>
@@ -10279,19 +10279,19 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB PARA PUBLICAÇÃO DE INFORMAÇÕES, NOTICIAS, VÍDEOS </t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE EXECUÇÃO DE SISTEMAS PRODAM-RH, PARA MANTER O CADASTRO DOS SERVIDORES E FOLHA DE PAGAMENTO DE PESSOAL, PROCESSAR FOLHAS DE PAGAMENTO E FORNECER RELA</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>2019NE01096</t>
+          <t>2019NE01095</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>3/2015</t>
+          <t>13/2017</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -10300,7 +10300,7 @@
         </is>
       </c>
       <c r="D339" t="n">
-        <v>6429.54</v>
+        <v>50813.46</v>
       </c>
       <c r="E339" t="inlineStr">
         <is>
@@ -10309,19 +10309,19 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE EXECUÇÃO DE SISTEMA, PARA PROCESSAMENTO DO SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPROWeb).</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE ACESSO A INTERNET ESTABELECENDO CIRCUITO DE DADOS, DESTINADO A ATENDER AS NECESSIDADES DESTE ÓRGÃO.</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>2019NE01095</t>
+          <t>2019NE01096</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>13/2017</t>
+          <t>3/2015</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -10330,7 +10330,7 @@
         </is>
       </c>
       <c r="D340" t="n">
-        <v>50813.46</v>
+        <v>6429.54</v>
       </c>
       <c r="E340" t="inlineStr">
         <is>
@@ -10339,19 +10339,19 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE ACESSO A INTERNET ESTABELECENDO CIRCUITO DE DADOS, DESTINADO A ATENDER AS NECESSIDADES DESTE ÓRGÃO.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE EXECUÇÃO DE SISTEMA, PARA PROCESSAMENTO DO SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPROWeb).</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>2019NE01097</t>
+          <t>2019NE01098</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>4/2015</t>
+          <t>16/2018</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -10360,7 +10360,7 @@
         </is>
       </c>
       <c r="D341" t="n">
-        <v>14867.31</v>
+        <v>3162.72</v>
       </c>
       <c r="E341" t="inlineStr">
         <is>
@@ -10369,19 +10369,19 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE EXECUÇÃO DE SISTEMAS PRODAM-RH, PARA MANTER O CADASTRO DOS SERVIDORES E FOLHA DE PAGAMENTO DE PESSOAL, PROCESSAR FOLHAS DE PAGAMENTO E FORNECER RELA</t>
+          <t xml:space="preserve">CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇO DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB PARA PUBLICAÇÃO DE INFORMAÇÕES, NOTICIAS, VÍDEOS </t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>2024NE0000880</t>
+          <t>2024NE0000879</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>7/2020</t>
+          <t>8/2020</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="D342" t="n">
-        <v>12635.82</v>
+        <v>2473.48</v>
       </c>
       <c r="E342" t="inlineStr">
         <is>
@@ -10399,7 +10399,7 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em manter o cadastro dos servidores e folha de pagamento pessoal, processar folhas de pagamento e fornecer relatórios para efetivação de pagamento. TC: 0007/2020 A</t>
+          <t>Contratação de Serviço de execução de sistema de protocolo em plataforma web, objetivando o controle e acompanhamento o controle e acompanhamento do registro de todos os documentos ou processos do cli</t>
         </is>
       </c>
     </row>
@@ -10436,12 +10436,12 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>2024NE0000879</t>
+          <t>2024NE0000880</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>8/2020</t>
+          <t>7/2020</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -10450,7 +10450,7 @@
         </is>
       </c>
       <c r="D344" t="n">
-        <v>2473.48</v>
+        <v>12635.82</v>
       </c>
       <c r="E344" t="inlineStr">
         <is>
@@ -10459,19 +10459,19 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Contratação de Serviço de execução de sistema de protocolo em plataforma web, objetivando o controle e acompanhamento o controle e acompanhamento do registro de todos os documentos ou processos do cli</t>
+          <t>Contratação de empresa especializada em manter o cadastro dos servidores e folha de pagamento pessoal, processar folhas de pagamento e fornecer relatórios para efetivação de pagamento. TC: 0007/2020 A</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>2022NE0000023</t>
+          <t>2022NE0000059</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>8/2020</t>
+          <t>13/2017</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -10480,7 +10480,7 @@
         </is>
       </c>
       <c r="D345" t="n">
-        <v>5337.38</v>
+        <v>71507</v>
       </c>
       <c r="E345" t="inlineStr">
         <is>
@@ -10489,19 +10489,19 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Contratação de Serviço de execução de sistema de protocolo em plataforma web, objetivando o controle e acompanhamento o controle e acompanhamento do registro de todos os documentos ou processos do cli</t>
+          <t>Contratação de empresa especializada em serviços de acesso a rede de internet, estabelecendo comunicação a partir de circuito de dados existentes entre a contratante e a contratada.</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>2022NE0000022</t>
+          <t>2022NE0000043</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>7/2020</t>
+          <t>16/2018</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="D346" t="n">
-        <v>12341.86</v>
+        <v>9838.76</v>
       </c>
       <c r="E346" t="inlineStr">
         <is>
@@ -10519,19 +10519,19 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em manter o cadastro dos servidores e folha de pagamento pessoal, processar folhas de pagamento e fornecer relatórios para efetivação de pagamento.</t>
+          <t>CONTRATAÇÃO DE SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB PARA PUBLICAÇÃO DE INFORMAÇÕES, NOTÍCIAS, VÍDEO E IMAGENS VIA WEBSITE.</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>2022NE0000043</t>
+          <t>2022NE0000022</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>16/2018</t>
+          <t>7/2020</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -10540,7 +10540,7 @@
         </is>
       </c>
       <c r="D347" t="n">
-        <v>9838.76</v>
+        <v>12341.86</v>
       </c>
       <c r="E347" t="inlineStr">
         <is>
@@ -10549,19 +10549,19 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB PARA PUBLICAÇÃO DE INFORMAÇÕES, NOTÍCIAS, VÍDEO E IMAGENS VIA WEBSITE.</t>
+          <t>Contratação de empresa especializada em manter o cadastro dos servidores e folha de pagamento pessoal, processar folhas de pagamento e fornecer relatórios para efetivação de pagamento.</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>2022NE0000059</t>
+          <t>2022NE0000023</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>13/2017</t>
+          <t>8/2020</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -10570,7 +10570,7 @@
         </is>
       </c>
       <c r="D348" t="n">
-        <v>71507</v>
+        <v>5337.38</v>
       </c>
       <c r="E348" t="inlineStr">
         <is>
@@ -10579,14 +10579,14 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviços de acesso a rede de internet, estabelecendo comunicação a partir de circuito de dados existentes entre a contratante e a contratada.</t>
+          <t>Contratação de Serviço de execução de sistema de protocolo em plataforma web, objetivando o controle e acompanhamento o controle e acompanhamento do registro de todos os documentos ou processos do cli</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>2019NE01391</t>
+          <t>2019NE01393</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -10600,7 +10600,7 @@
         </is>
       </c>
       <c r="D349" t="n">
-        <v>1357.56</v>
+        <v>1539.44</v>
       </c>
       <c r="E349" t="inlineStr">
         <is>
@@ -10609,14 +10609,14 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>RI Nº 36 DE 02/12/19 NF N° 5351 DE 30/11/18 EMPRESA ESPECIALIZADA EM SERVIÇOS DE EXECUÇÃO DE SISTEMAS PRODAM-RH, PARA MANTER O CADASTRO DOS SERVIDORES E FOLHA DE PAGAMENTO DE PESSOAL, PROCESSAR FOLHAS</t>
+          <t>RI Nº 38 DE 02/12/19 NF Nº 4698 DE 25/10/18 EMPRESA ESPECIALIZADA EM SERVIÇOS DE EXECUÇÃO DE SISTEMAS PRODAM-RH, PARA MANTER O CADASTRO DOS SERVIDORES E FOLHA DE PAGAMENTO DE PESSOAL, PROCESSAR FOLHAS</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>2019NE01395</t>
+          <t>2019NE01394</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -10639,19 +10639,19 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>EMPRESA ESPECIALIZADA EM SERVIÇO DE ACESSO A INTERNET ESTABELECENDO CIRCUITO DE DADOS, DESTINADO A ATENDER AS NECESSIDADES DESTE ÓRGÃO. NF Nº 4384 EMITIDA EM: 15/10/2018 NF Nº 4385 EMITIDA EM: 15/10/2</t>
+          <t>EMPRESA ESPECIALIZADA EM SERVIÇO DE ACESSO A INTERNET ESTABELECENDO CIRCUITO DE DADOS, DESTINADO A ATENDER AS NECESSIDADES DESTE ÓRGÃO. NF Nº 5490 EMITIDA EM: 05/12/2018 NF Nº 5491 EMITIDA EM: 05/12/2</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2019NE01392</t>
+          <t>2019NE01389</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>4/2015</t>
+          <t>3/2015</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -10660,7 +10660,7 @@
         </is>
       </c>
       <c r="D351" t="n">
-        <v>2626.44</v>
+        <v>959.51</v>
       </c>
       <c r="E351" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>RI Nº 37 DE 02/12/19 NF Nº 5659 DE 18/12/18 EMPRESA ESPECIALIZADA EM SERVIÇOS DE EXECUÇÃO DE SISTEMAS PRODAM-RH, PARA MANTER O CADASTRO DOS SERVIDORES E FOLHA DE PAGAMENTO DE PESSOAL, PROCESSAR FOLHAS</t>
+          <t>RD nº 034 de 02/12/2019, NF nº 5623 de 17/12/18 Empresa p/ serviços de Sist., p/ processamento do Sistema de Protoc. em plataforma Web (SPROWeb) obj. o controle e acomp. do regist. de todos os doc. ou</t>
         </is>
       </c>
     </row>
@@ -10706,12 +10706,12 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>2019NE01389</t>
+          <t>2019NE01392</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>3/2015</t>
+          <t>4/2015</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -10720,7 +10720,7 @@
         </is>
       </c>
       <c r="D353" t="n">
-        <v>959.51</v>
+        <v>2626.44</v>
       </c>
       <c r="E353" t="inlineStr">
         <is>
@@ -10729,14 +10729,14 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>RD nº 034 de 02/12/2019, NF nº 5623 de 17/12/18 Empresa p/ serviços de Sist., p/ processamento do Sistema de Protoc. em plataforma Web (SPROWeb) obj. o controle e acomp. do regist. de todos os doc. ou</t>
+          <t>RI Nº 37 DE 02/12/19 NF Nº 5659 DE 18/12/18 EMPRESA ESPECIALIZADA EM SERVIÇOS DE EXECUÇÃO DE SISTEMAS PRODAM-RH, PARA MANTER O CADASTRO DOS SERVIDORES E FOLHA DE PAGAMENTO DE PESSOAL, PROCESSAR FOLHAS</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>2019NE01394</t>
+          <t>2019NE01395</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -10759,14 +10759,14 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>EMPRESA ESPECIALIZADA EM SERVIÇO DE ACESSO A INTERNET ESTABELECENDO CIRCUITO DE DADOS, DESTINADO A ATENDER AS NECESSIDADES DESTE ÓRGÃO. NF Nº 5490 EMITIDA EM: 05/12/2018 NF Nº 5491 EMITIDA EM: 05/12/2</t>
+          <t>EMPRESA ESPECIALIZADA EM SERVIÇO DE ACESSO A INTERNET ESTABELECENDO CIRCUITO DE DADOS, DESTINADO A ATENDER AS NECESSIDADES DESTE ÓRGÃO. NF Nº 4384 EMITIDA EM: 15/10/2018 NF Nº 4385 EMITIDA EM: 15/10/2</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>2019NE01393</t>
+          <t>2019NE01391</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -10780,7 +10780,7 @@
         </is>
       </c>
       <c r="D355" t="n">
-        <v>1539.44</v>
+        <v>1357.56</v>
       </c>
       <c r="E355" t="inlineStr">
         <is>
@@ -10789,14 +10789,14 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>RI Nº 38 DE 02/12/19 NF Nº 4698 DE 25/10/18 EMPRESA ESPECIALIZADA EM SERVIÇOS DE EXECUÇÃO DE SISTEMAS PRODAM-RH, PARA MANTER O CADASTRO DOS SERVIDORES E FOLHA DE PAGAMENTO DE PESSOAL, PROCESSAR FOLHAS</t>
+          <t>RI Nº 36 DE 02/12/19 NF N° 5351 DE 30/11/18 EMPRESA ESPECIALIZADA EM SERVIÇOS DE EXECUÇÃO DE SISTEMAS PRODAM-RH, PARA MANTER O CADASTRO DOS SERVIDORES E FOLHA DE PAGAMENTO DE PESSOAL, PROCESSAR FOLHAS</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>2024NE0000870</t>
+          <t>2024NE0000869</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -10819,14 +10819,14 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Despesa com serviço de Fornecimento de circuito de transmissão de dados Circuito de Transmissão de Dados - 20 Mbps - (2.000 x 2,208.210) Acesso Gerenciado a Rede MundialAlocacao de endereco IPv4. Fatu</t>
+          <t>Despesa com serviço de Fornecimento de circuito de transmissao de dados Circuito de Transmissao de Dados - 20 Mbps - (2.000 x 2,208.210) Acesso Gerenciado a Rede MundialAlocacao de endereco IPv4. Fatu</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>2024NE0000866</t>
+          <t>2024NE0000867</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -10849,14 +10849,14 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conta cobrança no valor de R$ 23.44,12 (Vinte e três mil, trezentos e quarenta e quatro reais e doze centavos) referente ao mês de Julho/2023, contrato: 11/2023, contratada: PRODAM - PROCESSAMENTO DE </t>
+          <t xml:space="preserve">Conta cobrança no valor de R$ 23.344,12 (Vinte e três mil, trezentos e quarenta e quatro reais e doze centavos) referente ao mês de Agosto/2023, contrato: 011/2023, contratada: PRODAM - PROCESSAMENTO </t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>2024NE0000864</t>
+          <t>2024NE0000865</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -10879,14 +10879,14 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Pagamento no valor de R$ 23.344,12 (Vinte e três mil, trezentos e quarenta e quatro reais) referente ao mês de Novembro/2023, contrato: 011/2023 Vigência: 07/2023 a 07/2024. Valor Global R$ 280.129,44</t>
+          <t xml:space="preserve">pagamento de Conta cobrança no valor de R$ 23.344,12 (Vinte e três mil, trezentos e quarenta e quatro reais e doze centavos) referente ao mês de Dezembro/2023, contrato: 011/2023, Vigência: 07/2023 a </t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>2024NE0000865</t>
+          <t>2024NE0000864</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -10909,14 +10909,14 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t xml:space="preserve">pagamento de Conta cobrança no valor de R$ 23.344,12 (Vinte e três mil, trezentos e quarenta e quatro reais e doze centavos) referente ao mês de Dezembro/2023, contrato: 011/2023, Vigência: 07/2023 a </t>
+          <t>Pagamento no valor de R$ 23.344,12 (Vinte e três mil, trezentos e quarenta e quatro reais) referente ao mês de Novembro/2023, contrato: 011/2023 Vigência: 07/2023 a 07/2024. Valor Global R$ 280.129,44</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2024NE0000867</t>
+          <t>2024NE0000866</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -10939,14 +10939,14 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conta cobrança no valor de R$ 23.344,12 (Vinte e três mil, trezentos e quarenta e quatro reais e doze centavos) referente ao mês de Agosto/2023, contrato: 011/2023, contratada: PRODAM - PROCESSAMENTO </t>
+          <t xml:space="preserve">Conta cobrança no valor de R$ 23.44,12 (Vinte e três mil, trezentos e quarenta e quatro reais e doze centavos) referente ao mês de Julho/2023, contrato: 11/2023, contratada: PRODAM - PROCESSAMENTO DE </t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2024NE0000869</t>
+          <t>2024NE0000870</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -10969,19 +10969,19 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Despesa com serviço de Fornecimento de circuito de transmissao de dados Circuito de Transmissao de Dados - 20 Mbps - (2.000 x 2,208.210) Acesso Gerenciado a Rede MundialAlocacao de endereco IPv4. Fatu</t>
+          <t>Despesa com serviço de Fornecimento de circuito de transmissão de dados Circuito de Transmissão de Dados - 20 Mbps - (2.000 x 2,208.210) Acesso Gerenciado a Rede MundialAlocacao de endereco IPv4. Fatu</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>2023NE0000156</t>
+          <t>2023NE0000157</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>8/2020</t>
+          <t>7/2020</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -10990,7 +10990,7 @@
         </is>
       </c>
       <c r="D362" t="n">
-        <v>15910.12</v>
+        <v>2473.48</v>
       </c>
       <c r="E362" t="inlineStr">
         <is>
@@ -10999,19 +10999,19 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em manter o cadastro dos servidores e folha de pagamento pessoal, processar folhas de pagamento e fornecer relatórios para efetivação de pagamento.</t>
+          <t>Contratação de Serviço de execução de sistema de protocolo em plataforma web, objetivando o controle e acompanhamento o controle e acompanhamento do registro de todos os documentos ou processos do cli</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>2023NE0000157</t>
+          <t>2023NE0000156</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>7/2020</t>
+          <t>8/2020</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -11020,7 +11020,7 @@
         </is>
       </c>
       <c r="D363" t="n">
-        <v>2473.48</v>
+        <v>15910.12</v>
       </c>
       <c r="E363" t="inlineStr">
         <is>
@@ -11029,19 +11029,19 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Contratação de Serviço de execução de sistema de protocolo em plataforma web, objetivando o controle e acompanhamento o controle e acompanhamento do registro de todos os documentos ou processos do cli</t>
+          <t>Contratação de empresa especializada em manter o cadastro dos servidores e folha de pagamento pessoal, processar folhas de pagamento e fornecer relatórios para efetivação de pagamento.</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>2025NE0000016</t>
+          <t>2025NE0000002</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>7/2020</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -11050,7 +11050,7 @@
         </is>
       </c>
       <c r="D364" t="n">
-        <v>48195.96</v>
+        <v>12635.82</v>
       </c>
       <c r="E364" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de empresa especializada em serviço de acesso à rede de internet, para atender as necessidades do Instituto de Desenvolvimento Agropecuário e Florestal Sustentável do Estado do Amazonas – </t>
+          <t>Contratação de empresa especializada em manter o cadastro dos servidores e folha de pagamento pessoal, processar folhas de pagamento e fornecer relatórios para efetivação de pagamento. TC: 0007/2020 A</t>
         </is>
       </c>
     </row>
@@ -11096,12 +11096,12 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>2025NE0000002</t>
+          <t>2025NE0000016</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>7/2020</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -11110,7 +11110,7 @@
         </is>
       </c>
       <c r="D366" t="n">
-        <v>12635.82</v>
+        <v>48195.96</v>
       </c>
       <c r="E366" t="inlineStr">
         <is>
@@ -11119,19 +11119,19 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em manter o cadastro dos servidores e folha de pagamento pessoal, processar folhas de pagamento e fornecer relatórios para efetivação de pagamento. TC: 0007/2020 A</t>
+          <t xml:space="preserve">Contratação de empresa especializada em serviço de acesso à rede de internet, para atender as necessidades do Instituto de Desenvolvimento Agropecuário e Florestal Sustentável do Estado do Amazonas – </t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>2024NE0000013</t>
+          <t>2024NE0000022</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>7/2020</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -11140,7 +11140,7 @@
         </is>
       </c>
       <c r="D367" t="n">
-        <v>15910.12</v>
+        <v>46688.24</v>
       </c>
       <c r="E367" t="inlineStr">
         <is>
@@ -11149,19 +11149,19 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em manter o cadastro dos servidores e folha de pagamento pessoal, processar folhas de pagamento e fornecer relatórios para efetivação de pagamento. TC: 0007/2020 A</t>
+          <t xml:space="preserve">Contratação de empresa especializada em serviço de acesso à rede de internet, para atender as necessidades do Instituto de Desenvolvimento Agropecuário e Florestal Sustentável do Estado do Amazonas – </t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>2024NE0000024</t>
+          <t>2024NE0000003</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>1/2024</t>
+          <t>8/2020</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -11170,7 +11170,7 @@
         </is>
       </c>
       <c r="D368" t="n">
-        <v>5435.32</v>
+        <v>2473.48</v>
       </c>
       <c r="E368" t="inlineStr">
         <is>
@@ -11179,19 +11179,19 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação dos serviços de fornecimento de licença de uso de sistema de informação, disponibilizando o Gestor de Conteúdo Web para publicação de informações, not</t>
+          <t>Contratação de Serviço de execução de sistema de protocolo em plataforma web, objetivando o controle e acompanhamento o controle e acompanhamento do registro de todos os documentos ou processos do cli</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>2024NE0000003</t>
+          <t>2024NE0000024</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>8/2020</t>
+          <t>1/2024</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -11200,7 +11200,7 @@
         </is>
       </c>
       <c r="D369" t="n">
-        <v>2473.48</v>
+        <v>5435.32</v>
       </c>
       <c r="E369" t="inlineStr">
         <is>
@@ -11209,19 +11209,19 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>Contratação de Serviço de execução de sistema de protocolo em plataforma web, objetivando o controle e acompanhamento o controle e acompanhamento do registro de todos os documentos ou processos do cli</t>
+          <t>Contratação de empresa especializada na prestação dos serviços de fornecimento de licença de uso de sistema de informação, disponibilizando o Gestor de Conteúdo Web para publicação de informações, not</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>2024NE0000022</t>
+          <t>2024NE0000013</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>7/2020</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -11230,7 +11230,7 @@
         </is>
       </c>
       <c r="D370" t="n">
-        <v>46688.24</v>
+        <v>15910.12</v>
       </c>
       <c r="E370" t="inlineStr">
         <is>
@@ -11239,19 +11239,19 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de empresa especializada em serviço de acesso à rede de internet, para atender as necessidades do Instituto de Desenvolvimento Agropecuário e Florestal Sustentável do Estado do Amazonas – </t>
+          <t>Contratação de empresa especializada em manter o cadastro dos servidores e folha de pagamento pessoal, processar folhas de pagamento e fornecer relatórios para efetivação de pagamento. TC: 0007/2020 A</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>2023NE0000003</t>
+          <t>2023NE0000008</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>8/2020</t>
+          <t>13/2017</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -11260,7 +11260,7 @@
         </is>
       </c>
       <c r="D371" t="n">
-        <v>2335.68</v>
+        <v>71507</v>
       </c>
       <c r="E371" t="inlineStr">
         <is>
@@ -11269,19 +11269,19 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>Contratação de Serviço de execução de sistema de protocolo em plataforma web, objetivando o controle e acompanhamento o controle e acompanhamento do registro de todos os documentos ou processos do cli</t>
+          <t>Contratação de empresa especializada em serviços de acesso a rede de internet, estabelecendo comunicação a partir de circuito de dados existentes entre a contratante e a contratada.</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>2023NE0000005</t>
+          <t>2023NE0000006</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>7/2020</t>
+          <t>16/2018</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -11290,7 +11290,7 @@
         </is>
       </c>
       <c r="D372" t="n">
-        <v>15023.72</v>
+        <v>10683.92</v>
       </c>
       <c r="E372" t="inlineStr">
         <is>
@@ -11299,19 +11299,19 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em manter o cadastro dos servidores e folha de pagamento pessoal, processar folhas de pagamento e fornecer relatórios para efetivação de pagamento.</t>
+          <t>CONTRATAÇÃO DE SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB PARA PUBLICAÇÃO DE INFORMAÇÕES, NOTÍCIAS, VÍDEO E IMAGENS VIA WEBSITE.</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>2023NE0000006</t>
+          <t>2023NE0000005</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>16/2018</t>
+          <t>7/2020</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -11320,7 +11320,7 @@
         </is>
       </c>
       <c r="D373" t="n">
-        <v>10683.92</v>
+        <v>15023.72</v>
       </c>
       <c r="E373" t="inlineStr">
         <is>
@@ -11329,19 +11329,19 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB PARA PUBLICAÇÃO DE INFORMAÇÕES, NOTÍCIAS, VÍDEO E IMAGENS VIA WEBSITE.</t>
+          <t>Contratação de empresa especializada em manter o cadastro dos servidores e folha de pagamento pessoal, processar folhas de pagamento e fornecer relatórios para efetivação de pagamento.</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>2023NE0000008</t>
+          <t>2023NE0000003</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>13/2017</t>
+          <t>8/2020</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -11350,7 +11350,7 @@
         </is>
       </c>
       <c r="D374" t="n">
-        <v>71507</v>
+        <v>2335.68</v>
       </c>
       <c r="E374" t="inlineStr">
         <is>
@@ -11359,19 +11359,19 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviços de acesso a rede de internet, estabelecendo comunicação a partir de circuito de dados existentes entre a contratante e a contratada.</t>
+          <t>Contratação de Serviço de execução de sistema de protocolo em plataforma web, objetivando o controle e acompanhamento o controle e acompanhamento do registro de todos os documentos ou processos do cli</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>2020NE00008</t>
+          <t>2020NE00010</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>3/2015</t>
+          <t>13/2017</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -11380,7 +11380,7 @@
         </is>
       </c>
       <c r="D375" t="n">
-        <v>2143.18</v>
+        <v>84689.10000000001</v>
       </c>
       <c r="E375" t="inlineStr">
         <is>
@@ -11389,19 +11389,19 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>Contratação de empresa p/ serviços de Sist., p/ processamento do Sistema de Protoc. em plataforma Web (SPROWEB) obj. o controle e acomp. do regist. de todos os doc. ou processos dos clientes.</t>
+          <t>Contratação de empresa especializada em serviços de acesso a rede de internet, estabelecendo comunicação a partir de circuito de dados existentes entre a contratante e a contratada.</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>2020NE00009</t>
+          <t>2020NE00007</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>16/2018</t>
+          <t>4/2015</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -11410,7 +11410,7 @@
         </is>
       </c>
       <c r="D376" t="n">
-        <v>18257.8</v>
+        <v>4955.77</v>
       </c>
       <c r="E376" t="inlineStr">
         <is>
@@ -11419,19 +11419,19 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB PARA PUBLICAÇÃO DE INFORMAÇÕES, NOTÍCIAS, VÍDEO E IMAGENS VIA WEBSITE.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE EXECUÇÃO DE SISTEMAS PRODAM-RH, PARA MANTER O CADASTRO DOS SERVIDORES E FOLHA DE PAGAMENTO DE PESSOAL, PROCESSAR FOLHAS DE PAGAMENTO E FORNECER RELA</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>2020NE00007</t>
+          <t>2020NE00009</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>4/2015</t>
+          <t>16/2018</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -11440,7 +11440,7 @@
         </is>
       </c>
       <c r="D377" t="n">
-        <v>4955.77</v>
+        <v>18257.8</v>
       </c>
       <c r="E377" t="inlineStr">
         <is>
@@ -11449,19 +11449,19 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA EM SERVIÇOS DE EXECUÇÃO DE SISTEMAS PRODAM-RH, PARA MANTER O CADASTRO DOS SERVIDORES E FOLHA DE PAGAMENTO DE PESSOAL, PROCESSAR FOLHAS DE PAGAMENTO E FORNECER RELA</t>
+          <t>CONTRATAÇÃO DE SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB PARA PUBLICAÇÃO DE INFORMAÇÕES, NOTÍCIAS, VÍDEO E IMAGENS VIA WEBSITE.</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>2020NE00010</t>
+          <t>2020NE00008</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>13/2017</t>
+          <t>3/2015</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -11470,7 +11470,7 @@
         </is>
       </c>
       <c r="D378" t="n">
-        <v>84689.10000000001</v>
+        <v>2143.18</v>
       </c>
       <c r="E378" t="inlineStr">
         <is>
@@ -11479,28 +11479,24 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviços de acesso a rede de internet, estabelecendo comunicação a partir de circuito de dados existentes entre a contratante e a contratada.</t>
+          <t>Contratação de empresa p/ serviços de Sist., p/ processamento do Sistema de Protoc. em plataforma Web (SPROWEB) obj. o controle e acomp. do regist. de todos os doc. ou processos dos clientes.</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>2019NE00009</t>
-        </is>
-      </c>
-      <c r="B379" t="inlineStr">
-        <is>
-          <t>4/2015</t>
-        </is>
-      </c>
+          <t>2019NE00026</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr"/>
       <c r="C379" t="inlineStr">
         <is>
           <t>02/01/2019</t>
         </is>
       </c>
       <c r="D379" t="n">
-        <v>4517.98</v>
+        <v>1934.28</v>
       </c>
       <c r="E379" t="inlineStr">
         <is>
@@ -11509,28 +11505,24 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>Contratação de serviço de execução de sistemas PRODAM - RH, para manter o cadastro dos servidores e Folha de Pagamento de Pessoal, processar folhas de pagamento e fornecer relatórios para efetivação d</t>
+          <t>-ANULAÇÃO QUE SE FAZ DA NOTA DE EMPENHO EM VIRTUDE NO EQUIVOCO NA DESCRIÇÃO.</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>2019NE00008</t>
-        </is>
-      </c>
-      <c r="B380" t="inlineStr">
-        <is>
-          <t>23/2015</t>
-        </is>
-      </c>
+          <t>2019NE00025</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr"/>
       <c r="C380" t="inlineStr">
         <is>
           <t>02/01/2019</t>
         </is>
       </c>
       <c r="D380" t="n">
-        <v>119765.85</v>
+        <v>46932.24</v>
       </c>
       <c r="E380" t="inlineStr">
         <is>
@@ -11539,19 +11531,19 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>Contratação de serviços de sistemas de informação, compreendendo o desenvolvimento e implantação do sistema de Gestão e Fomento de Assist.Téc.,Ext.Rural e Florestal - ATER</t>
+          <t>-ANULAÇÃO QUE SE FAZ DA NOTA DE EMPENHO EM VIRTUDE NO EQUIVOCO NA DESCRIÇÃO.</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>2019NE00010</t>
+          <t>2019NE00030</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>16/2018</t>
+          <t>3/2015</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -11560,7 +11552,7 @@
         </is>
       </c>
       <c r="D381" t="n">
-        <v>4744.08</v>
+        <v>1934.28</v>
       </c>
       <c r="E381" t="inlineStr">
         <is>
@@ -11569,14 +11561,14 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB PARA PUBLICAÇÃO DE INFORMAÇÕES, NOTÍCIAS, VÍDEO E IMAGENS VIA WEBSITE.</t>
+          <t>Contratação de empresa p/ serviços de Sist., p/ processamento do Sistema de Protoc. em plataforma Web (SPROWeb) obj. o controle e acomp. do regist. de todos os doc. ou processos dos clientes.</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>2019NE00004</t>
+          <t>2019NE00029</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -11636,7 +11628,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>2019NE00029</t>
+          <t>2019NE00004</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -11666,12 +11658,12 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2019NE00030</t>
+          <t>2019NE00010</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>3/2015</t>
+          <t>16/2018</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -11680,7 +11672,7 @@
         </is>
       </c>
       <c r="D385" t="n">
-        <v>1934.28</v>
+        <v>4744.08</v>
       </c>
       <c r="E385" t="inlineStr">
         <is>
@@ -11689,24 +11681,28 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>Contratação de empresa p/ serviços de Sist., p/ processamento do Sistema de Protoc. em plataforma Web (SPROWeb) obj. o controle e acomp. do regist. de todos os doc. ou processos dos clientes.</t>
+          <t>CONTRATAÇÃO DE SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB PARA PUBLICAÇÃO DE INFORMAÇÕES, NOTÍCIAS, VÍDEO E IMAGENS VIA WEBSITE.</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>2019NE00025</t>
-        </is>
-      </c>
-      <c r="B386" t="inlineStr"/>
+          <t>2019NE00008</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>23/2015</t>
+        </is>
+      </c>
       <c r="C386" t="inlineStr">
         <is>
           <t>02/01/2019</t>
         </is>
       </c>
       <c r="D386" t="n">
-        <v>46932.24</v>
+        <v>119765.85</v>
       </c>
       <c r="E386" t="inlineStr">
         <is>
@@ -11715,24 +11711,28 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>-ANULAÇÃO QUE SE FAZ DA NOTA DE EMPENHO EM VIRTUDE NO EQUIVOCO NA DESCRIÇÃO.</t>
+          <t>Contratação de serviços de sistemas de informação, compreendendo o desenvolvimento e implantação do sistema de Gestão e Fomento de Assist.Téc.,Ext.Rural e Florestal - ATER</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2019NE00026</t>
-        </is>
-      </c>
-      <c r="B387" t="inlineStr"/>
+          <t>2019NE00009</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>4/2015</t>
+        </is>
+      </c>
       <c r="C387" t="inlineStr">
         <is>
           <t>02/01/2019</t>
         </is>
       </c>
       <c r="D387" t="n">
-        <v>1934.28</v>
+        <v>4517.98</v>
       </c>
       <c r="E387" t="inlineStr">
         <is>
@@ -11741,19 +11741,19 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>-ANULAÇÃO QUE SE FAZ DA NOTA DE EMPENHO EM VIRTUDE NO EQUIVOCO NA DESCRIÇÃO.</t>
+          <t>Contratação de serviço de execução de sistemas PRODAM - RH, para manter o cadastro dos servidores e Folha de Pagamento de Pessoal, processar folhas de pagamento e fornecer relatórios para efetivação d</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>2018NE00035</t>
+          <t>2018NE00036</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>17/2014</t>
+          <t>3/2015</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -11762,7 +11762,7 @@
         </is>
       </c>
       <c r="D388" t="n">
-        <v>10257.48</v>
+        <v>1934.28</v>
       </c>
       <c r="E388" t="inlineStr">
         <is>
@@ -11771,19 +11771,19 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>-REFERENTE AO TERCEIRO TERMO ADITIVO AO TERMO DE CONTRATO Nº 017/2014 FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS-IDAM E A EMPRESA: PRODAM P</t>
+          <t>-REFERENTE AO SALDO DO SEGUNDO TERMO ADITIVO AO TERMO DE CONTRATO DE Nº 003/2015, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS - IDAM E A EMP</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>2018NE00037</t>
+          <t>2018NE00032</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>4/2015</t>
+          <t>13/2017</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -11792,7 +11792,7 @@
         </is>
       </c>
       <c r="D389" t="n">
-        <v>4517.98</v>
+        <v>63000</v>
       </c>
       <c r="E389" t="inlineStr">
         <is>
@@ -11801,19 +11801,19 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>-REFERENTE AO SALDO DO SEGUNDO TERMO ADITIVO AO TERMO DE CONTRATO Nº 004/2015, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS - IDAM E A EMPRES</t>
+          <t xml:space="preserve">-REFERENTE A UM TERMO DE CONTRATO Nº 013/2017 FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS - IDAM E A EMPRESA: PRODAM PROCESSAMENTO DE DADOS </t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>2018NE00032</t>
+          <t>2018NE00037</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>13/2017</t>
+          <t>4/2015</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -11822,7 +11822,7 @@
         </is>
       </c>
       <c r="D390" t="n">
-        <v>63000</v>
+        <v>4517.98</v>
       </c>
       <c r="E390" t="inlineStr">
         <is>
@@ -11831,19 +11831,19 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t xml:space="preserve">-REFERENTE A UM TERMO DE CONTRATO Nº 013/2017 FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS - IDAM E A EMPRESA: PRODAM PROCESSAMENTO DE DADOS </t>
+          <t>-REFERENTE AO SALDO DO SEGUNDO TERMO ADITIVO AO TERMO DE CONTRATO Nº 004/2015, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS - IDAM E A EMPRES</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>2018NE00036</t>
+          <t>2018NE00035</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>3/2015</t>
+          <t>17/2014</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -11852,7 +11852,7 @@
         </is>
       </c>
       <c r="D391" t="n">
-        <v>1934.28</v>
+        <v>10257.48</v>
       </c>
       <c r="E391" t="inlineStr">
         <is>
@@ -11861,19 +11861,19 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>-REFERENTE AO SALDO DO SEGUNDO TERMO ADITIVO AO TERMO DE CONTRATO DE Nº 003/2015, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS - IDAM E A EMP</t>
+          <t>-REFERENTE AO TERCEIRO TERMO ADITIVO AO TERMO DE CONTRATO Nº 017/2014 FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS-IDAM E A EMPRESA: PRODAM P</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>2017NE00048</t>
+          <t>2017NE00004</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>23/2015</t>
+          <t>8/2012</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -11882,7 +11882,7 @@
         </is>
       </c>
       <c r="D392" t="n">
-        <v>159687.8</v>
+        <v>14030.26</v>
       </c>
       <c r="E392" t="inlineStr">
         <is>
@@ -11891,19 +11891,19 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>-REFERENTE A PARTE DO PRIMEIRO TERMO ADITIVO AO TERMO DE CONTRATO DE Nº 023/2015, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS-IDAM E A EMPRE</t>
+          <t>-REFERENTE AO SALDO DO QUARTO TERMO ADITIVO AO TERMO DE CONTRATO Nº 008/2012 FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS - IDAM E A EMPRESA:</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>2017NE00005</t>
+          <t>2017NE00008</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>17/2014</t>
+          <t>14/2013</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -11912,7 +11912,7 @@
         </is>
       </c>
       <c r="D393" t="n">
-        <v>4488.4</v>
+        <v>24480</v>
       </c>
       <c r="E393" t="inlineStr">
         <is>
@@ -11921,19 +11921,19 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>-REFERENTE A PARTE DO SEGUNDO TERMO ADITIVO AO DO TERMO DE CONTRATO Nº 017/2014 FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS-IDAM E A EMPRESA</t>
+          <t>-REFERENTE A PARTE DO TERCEIRO TERMO ADITIVO AO TERMO DE CONTRATO Nº 014/2013, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS-IDAM E A EMPRESA:</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>2017NE00007</t>
+          <t>2017NE00006</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>4/2015</t>
+          <t>3/2015</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -11942,7 +11942,7 @@
         </is>
       </c>
       <c r="D394" t="n">
-        <v>4517.98</v>
+        <v>1805.55</v>
       </c>
       <c r="E394" t="inlineStr">
         <is>
@@ -11951,19 +11951,19 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>Contratação de serviço de execução de sistemas PRODAM - RH, para manter o cadastro dos servidores e Folha de Pagamento de Pessoal, processar folhas de pagamento e fornecer relatórios para efetivação d</t>
+          <t>-REFERENTE AO SALDO DO PRIMEIRO TERMO ADITIVO AO TERMO DE CONTRATO DE Nº 003/2015, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS - IDAM E A EM</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>2017NE00006</t>
+          <t>2017NE00007</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>3/2015</t>
+          <t>4/2015</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -11972,7 +11972,7 @@
         </is>
       </c>
       <c r="D395" t="n">
-        <v>1805.55</v>
+        <v>4517.98</v>
       </c>
       <c r="E395" t="inlineStr">
         <is>
@@ -11981,19 +11981,19 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>-REFERENTE AO SALDO DO PRIMEIRO TERMO ADITIVO AO TERMO DE CONTRATO DE Nº 003/2015, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS - IDAM E A EM</t>
+          <t>Contratação de serviço de execução de sistemas PRODAM - RH, para manter o cadastro dos servidores e Folha de Pagamento de Pessoal, processar folhas de pagamento e fornecer relatórios para efetivação d</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>2017NE00008</t>
+          <t>2017NE00005</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>14/2013</t>
+          <t>17/2014</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -12002,7 +12002,7 @@
         </is>
       </c>
       <c r="D396" t="n">
-        <v>24480</v>
+        <v>4488.4</v>
       </c>
       <c r="E396" t="inlineStr">
         <is>
@@ -12011,19 +12011,19 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>-REFERENTE A PARTE DO TERCEIRO TERMO ADITIVO AO TERMO DE CONTRATO Nº 014/2013, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS-IDAM E A EMPRESA:</t>
+          <t>-REFERENTE A PARTE DO SEGUNDO TERMO ADITIVO AO DO TERMO DE CONTRATO Nº 017/2014 FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS-IDAM E A EMPRESA</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>2017NE00004</t>
+          <t>2017NE00048</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>8/2012</t>
+          <t>23/2015</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -12032,7 +12032,7 @@
         </is>
       </c>
       <c r="D397" t="n">
-        <v>14030.26</v>
+        <v>159687.8</v>
       </c>
       <c r="E397" t="inlineStr">
         <is>
@@ -12041,19 +12041,19 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>-REFERENTE AO SALDO DO QUARTO TERMO ADITIVO AO TERMO DE CONTRATO Nº 008/2012 FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS - IDAM E A EMPRESA:</t>
+          <t>-REFERENTE A PARTE DO PRIMEIRO TERMO ADITIVO AO TERMO DE CONTRATO DE Nº 023/2015, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS-IDAM E A EMPRE</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>2014NE00039</t>
+          <t>2014NE00063</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>2/2010</t>
+          <t>12/2011</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -12062,7 +12062,7 @@
         </is>
       </c>
       <c r="D398" t="n">
-        <v>29150.28</v>
+        <v>3000</v>
       </c>
       <c r="E398" t="inlineStr">
         <is>
@@ -12071,19 +12071,19 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>Contrato No. 2/2010 - CFPP-Cad. e Folha de Pagto. de Pessoal</t>
+          <t>Contrato No. 12/2011 - Serviços Eventuais de Informatica</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>2014NE00042</t>
+          <t>2014NE00040</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>14/2013</t>
+          <t>3/2010</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -12092,7 +12092,7 @@
         </is>
       </c>
       <c r="D399" t="n">
-        <v>46645.36</v>
+        <v>1500</v>
       </c>
       <c r="E399" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>Contrato No. 14/2013 - Serviços de Rede</t>
+          <t>Contrato No. 3/2010 - Cessão de uso do Sistema SPROWeb</t>
         </is>
       </c>
     </row>
@@ -12138,12 +12138,12 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>2014NE00040</t>
+          <t>2014NE00042</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>3/2010</t>
+          <t>14/2013</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -12152,7 +12152,7 @@
         </is>
       </c>
       <c r="D401" t="n">
-        <v>1500</v>
+        <v>46645.36</v>
       </c>
       <c r="E401" t="inlineStr">
         <is>
@@ -12161,19 +12161,19 @@
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>Contrato No. 3/2010 - Cessão de uso do Sistema SPROWeb</t>
+          <t>Contrato No. 14/2013 - Serviços de Rede</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>2014NE00063</t>
+          <t>2014NE00039</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>12/2011</t>
+          <t>2/2010</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -12182,7 +12182,7 @@
         </is>
       </c>
       <c r="D402" t="n">
-        <v>3000</v>
+        <v>29150.28</v>
       </c>
       <c r="E402" t="inlineStr">
         <is>
@@ -12191,7 +12191,7 @@
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>Contrato No. 12/2011 - Serviços Eventuais de Informatica</t>
+          <t>Contrato No. 2/2010 - CFPP-Cad. e Folha de Pagto. de Pessoal</t>
         </is>
       </c>
     </row>
@@ -12228,12 +12228,12 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>2025NE0000967</t>
+          <t>2025NE0000968</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>5/2025</t>
+          <t>6/2025</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -12242,7 +12242,7 @@
         </is>
       </c>
       <c r="D404" t="n">
-        <v>2748.84</v>
+        <v>17149.2</v>
       </c>
       <c r="E404" t="inlineStr">
         <is>
@@ -12251,7 +12251,7 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de execução de sistema de protocolo web visando atender às necessidades do IDAM central.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de execução e manutenção de sistema de Recursos Humanos (RH), para atender as necessidades do IDAM, pelo período de 12 (doze) meses</t>
         </is>
       </c>
     </row>
@@ -12288,12 +12288,12 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>2025NE0000968</t>
+          <t>2025NE0000967</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>6/2025</t>
+          <t>5/2025</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -12302,7 +12302,7 @@
         </is>
       </c>
       <c r="D406" t="n">
-        <v>17149.2</v>
+        <v>2748.84</v>
       </c>
       <c r="E406" t="inlineStr">
         <is>
@@ -12311,19 +12311,19 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de execução e manutenção de sistema de Recursos Humanos (RH), para atender as necessidades do IDAM, pelo período de 12 (doze) meses</t>
+          <t>Contratação de empresa especializada na prestação de serviços de execução de sistema de protocolo web visando atender às necessidades do IDAM central.</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>2024NE0000140</t>
+          <t>2024NE0000139</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>1/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -12332,7 +12332,7 @@
         </is>
       </c>
       <c r="D407" t="n">
-        <v>5435.32</v>
+        <v>46688.24</v>
       </c>
       <c r="E407" t="inlineStr">
         <is>
@@ -12341,19 +12341,19 @@
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação dos serviços de fornecimento de licença de uso de sistema de informação, disponibilizando o Gestor de Conteúdo Web para publicação de informações, not</t>
+          <t xml:space="preserve">Contratação de empresa especializada em serviço de acesso à rede de internet, para atender as necessidades do Instituto de Desenvolvimento Agropecuário e Florestal Sustentável do Estado do Amazonas – </t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>2024NE0000139</t>
+          <t>2024NE0000140</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>1/2024</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -12362,7 +12362,7 @@
         </is>
       </c>
       <c r="D408" t="n">
-        <v>46688.24</v>
+        <v>5435.32</v>
       </c>
       <c r="E408" t="inlineStr">
         <is>
@@ -12371,19 +12371,19 @@
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de empresa especializada em serviço de acesso à rede de internet, para atender as necessidades do Instituto de Desenvolvimento Agropecuário e Florestal Sustentável do Estado do Amazonas – </t>
+          <t>Contratação de empresa especializada na prestação dos serviços de fornecimento de licença de uso de sistema de informação, disponibilizando o Gestor de Conteúdo Web para publicação de informações, not</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>2018NE00336</t>
+          <t>2018NE00339</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>17/2014</t>
+          <t>3/2015</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -12392,7 +12392,7 @@
         </is>
       </c>
       <c r="D409" t="n">
-        <v>10257.48</v>
+        <v>21277.08</v>
       </c>
       <c r="E409" t="inlineStr">
         <is>
@@ -12401,19 +12401,19 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>-REFERENTE AO TERCEIRO TERMO ADITIVO AO TERMO DE CONTRATO Nº 017/2014 FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS-IDAM E A EMPRESA: PRODAM P</t>
+          <t>-REFERENTE A PARTE DO TERCEIRO TERMO ADITIVO AO TERMO DE CONTRATO DE Nº 003/2015, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS - IDAM E A EMP</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>2018NE00334</t>
+          <t>2018NE00340</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>4/2015</t>
+          <t>23/2015</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -12422,7 +12422,7 @@
         </is>
       </c>
       <c r="D410" t="n">
-        <v>4517.98</v>
+        <v>39921.95</v>
       </c>
       <c r="E410" t="inlineStr">
         <is>
@@ -12431,19 +12431,19 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>-REFERENTE AO SALDO DO SEGUNDO TERMO ADITIVO AO TERMO DE CONTRATO Nº 004/2015, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS - IDAM E A EMPRES</t>
+          <t>Contratação de empresa especializada em Sistemas de Gestão, compreendendo o desenvolvimento e implantação do sistema de Gestão e Fomento de Assist.Téc.,Ext.Rural e Florestal, deste IDAM.Contrato nº 23</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>2018NE00338</t>
+          <t>2018NE00335</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>4/2015</t>
+          <t>13/2017</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -12452,7 +12452,7 @@
         </is>
       </c>
       <c r="D411" t="n">
-        <v>49697.78</v>
+        <v>63000</v>
       </c>
       <c r="E411" t="inlineStr">
         <is>
@@ -12461,7 +12461,7 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>-REFERENTE A PARTE DO TERCEIRO TERMO ADITIVO AO TERMO DE CONTRATO Nº 004/2015, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS - IDAM E A EMPRES</t>
+          <t xml:space="preserve">-REFERENTE A UM TERMO DE CONTRATO Nº 013/2017 FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS - IDAM E A EMPRESA: PRODAM PROCESSAMENTO DE DADOS </t>
         </is>
       </c>
     </row>
@@ -12498,12 +12498,12 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>2018NE00335</t>
+          <t>2018NE00338</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>13/2017</t>
+          <t>4/2015</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -12512,7 +12512,7 @@
         </is>
       </c>
       <c r="D413" t="n">
-        <v>63000</v>
+        <v>49697.78</v>
       </c>
       <c r="E413" t="inlineStr">
         <is>
@@ -12521,19 +12521,19 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t xml:space="preserve">-REFERENTE A UM TERMO DE CONTRATO Nº 013/2017 FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUÁRIO E FLORESTAL SUSTENTÁVEL DO ESTADO DO AMAZONAS - IDAM E A EMPRESA: PRODAM PROCESSAMENTO DE DADOS </t>
+          <t>-REFERENTE A PARTE DO TERCEIRO TERMO ADITIVO AO TERMO DE CONTRATO Nº 004/2015, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS - IDAM E A EMPRES</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>2018NE00340</t>
+          <t>2018NE00334</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>23/2015</t>
+          <t>4/2015</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -12542,7 +12542,7 @@
         </is>
       </c>
       <c r="D414" t="n">
-        <v>39921.95</v>
+        <v>4517.98</v>
       </c>
       <c r="E414" t="inlineStr">
         <is>
@@ -12551,19 +12551,19 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em Sistemas de Gestão, compreendendo o desenvolvimento e implantação do sistema de Gestão e Fomento de Assist.Téc.,Ext.Rural e Florestal, deste IDAM.Contrato nº 23</t>
+          <t>-REFERENTE AO SALDO DO SEGUNDO TERMO ADITIVO AO TERMO DE CONTRATO Nº 004/2015, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS - IDAM E A EMPRES</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>2018NE00339</t>
+          <t>2018NE00336</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>3/2015</t>
+          <t>17/2014</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -12572,7 +12572,7 @@
         </is>
       </c>
       <c r="D415" t="n">
-        <v>21277.08</v>
+        <v>10257.48</v>
       </c>
       <c r="E415" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>-REFERENTE A PARTE DO TERCEIRO TERMO ADITIVO AO TERMO DE CONTRATO DE Nº 003/2015, FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS - IDAM E A EMP</t>
+          <t>-REFERENTE AO TERCEIRO TERMO ADITIVO AO TERMO DE CONTRATO Nº 017/2014 FIRMADO ENTRE O INSTITUTO DE DESENVOLVIMENTO AGROPECUARIO E FLORESTAL SUSTENTAVEL DO ESTADO DO AMAZONAS-IDAM E A EMPRESA: PRODAM P</t>
         </is>
       </c>
     </row>

--- a/DOSSIES_MULTIFORMATO/IDAM/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/IDAM/dossie.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2028-06-30</t>
         </is>
       </c>
     </row>
